--- a/ptr_equity.xlsx
+++ b/ptr_equity.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,63 +444,63 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>43890</v>
+        <v>39507</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.007014036987233432</v>
       </c>
       <c r="C2" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.007014036987233</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>43921</v>
+        <v>39538</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.007853313135982663</v>
       </c>
       <c r="C3" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.014922433552024</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>43951</v>
+        <v>39568</v>
       </c>
       <c r="B4" t="n">
-        <v>0.001646840732779033</v>
+        <v>-0.01241396782531058</v>
       </c>
       <c r="C4" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.001646840732779</v>
+        <v>1.002323219116723</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>43982</v>
+        <v>39599</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.001646840732779</v>
+        <v>1.002323219116723</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44012</v>
+        <v>39629</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -509,68 +509,68 @@
         <v>0.625</v>
       </c>
       <c r="D6" t="n">
-        <v>1.001646840732779</v>
+        <v>1.002323219116723</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44043</v>
+        <v>39660</v>
       </c>
       <c r="B7" t="n">
-        <v>0.005379538489170077</v>
+        <v>0.005206621403512517</v>
       </c>
       <c r="C7" t="n">
         <v>0.625</v>
       </c>
       <c r="D7" t="n">
-        <v>1.007035238465057</v>
+        <v>1.007541936642614</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44074</v>
+        <v>39691</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.006061762753619064</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0.625</v>
       </c>
       <c r="D8" t="n">
-        <v>1.000930829764947</v>
+        <v>1.007541936642614</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44104</v>
+        <v>39721</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001966640958531235</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0.625</v>
       </c>
       <c r="D9" t="n">
-        <v>1.00289930133142</v>
+        <v>1.007541936642614</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44135</v>
+        <v>39752</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>-0.006265065059176272</v>
       </c>
       <c r="C10" t="n">
         <v>0.625</v>
       </c>
       <c r="D10" t="n">
-        <v>1.00289930133142</v>
+        <v>1.0012296208597</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44165</v>
+        <v>39782</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -579,26 +579,26 @@
         <v>0.625</v>
       </c>
       <c r="D11" t="n">
-        <v>1.00289930133142</v>
+        <v>1.0012296208597</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44196</v>
+        <v>39813</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.001478081678608488</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0.625</v>
       </c>
       <c r="D12" t="n">
-        <v>1.001416934248633</v>
+        <v>1.0012296208597</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44227</v>
+        <v>39844</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
@@ -607,12 +607,12 @@
         <v>0.625</v>
       </c>
       <c r="D13" t="n">
-        <v>1.001416934248633</v>
+        <v>1.0012296208597</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44255</v>
+        <v>39872</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -621,875 +621,2891 @@
         <v>0.625</v>
       </c>
       <c r="D14" t="n">
-        <v>1.001416934248633</v>
+        <v>1.0012296208597</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44286</v>
+        <v>39903</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="D15" t="n">
-        <v>1.001416934248633</v>
+        <v>1.0012296208597</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44316</v>
+        <v>39933</v>
       </c>
       <c r="B16" t="n">
-        <v>0.003754544125118091</v>
+        <v>-0.0169283794220732</v>
       </c>
       <c r="C16" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="D16" t="n">
-        <v>1.005176798315909</v>
+        <v>0.9842804259491681</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44347</v>
+        <v>39964</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="D17" t="n">
-        <v>1.005176798315909</v>
+        <v>0.9842804259491681</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44377</v>
+        <v>39994</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="D18" t="n">
-        <v>1.005176798315909</v>
+        <v>0.9842804259491681</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44408</v>
+        <v>40025</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.004961852745142949</v>
       </c>
       <c r="C19" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="D19" t="n">
-        <v>1.005176798315909</v>
+        <v>0.9891642804826545</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>44439</v>
+        <v>40056</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.005032885895329139</v>
       </c>
       <c r="C20" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="D20" t="n">
-        <v>1.005176798315909</v>
+        <v>0.9941426314380591</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>44469</v>
+        <v>40086</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.005920651679574998</v>
+        <v>0.007125589171385832</v>
       </c>
       <c r="C21" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9992254966166906</v>
+        <v>1.001226483407447</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>44500</v>
+        <v>40117</v>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9992254966166906</v>
+        <v>1.001226483407447</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>44530</v>
+        <v>40147</v>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9992254966166906</v>
+        <v>1.001226483407447</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>44561</v>
+        <v>40178</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.001965244189163455</v>
+        <v>-0.02740258534306548</v>
       </c>
       <c r="C24" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9972617745158007</v>
+        <v>0.9737902892481372</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>44592</v>
+        <v>40209</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.007923967249957243</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0.375</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9893595048749032</v>
+        <v>0.9737902892481372</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>44620</v>
+        <v>40237</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.001277140052225087</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>0.375</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9880959542251778</v>
+        <v>0.9737902892481372</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>44651</v>
+        <v>40268</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.01494109243217163</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9733327212412446</v>
+        <v>0.9737902892481372</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>44681</v>
+        <v>40298</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.00592475484501152</v>
       </c>
       <c r="C28" t="n">
         <v>0.375</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9733327212412446</v>
+        <v>0.9795597579823851</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>44712</v>
+        <v>40329</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9733327212412446</v>
+        <v>0.9795597579823851</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>44742</v>
+        <v>40359</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.00275270495829762</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9706534234334105</v>
+        <v>0.9795597579823851</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>44773</v>
+        <v>40390</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9706534234334105</v>
+        <v>0.9795597579823851</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>44804</v>
+        <v>40421</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.375</v>
+        <v>0.6370460448606655</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9706534234334105</v>
+        <v>0.9795597579823851</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>44834</v>
+        <v>40451</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.01414552827598421</v>
+        <v>-1.913591707205205e-05</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3280870290053974</v>
+        <v>0.6283573921782999</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9569230179860523</v>
+        <v>0.9795410132080893</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>44865</v>
+        <v>40482</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.004825646055679007</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3975944690076606</v>
+        <v>0.6019420669213249</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9523052461987194</v>
+        <v>0.9795410132080893</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>44895</v>
+        <v>40512</v>
       </c>
       <c r="B35" t="n">
-        <v>0.01626649524008552</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3977832392128828</v>
+        <v>0.6131522648752805</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9677959149531193</v>
+        <v>0.9795410132080893</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>44926</v>
+        <v>40543</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>-0.02179889272121318</v>
       </c>
       <c r="C36" t="n">
-        <v>0.336941265703624</v>
+        <v>0.633041522104832</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9677959149531193</v>
+        <v>0.9581881037451377</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>44957</v>
+        <v>40574</v>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>-0.0001287348913950908</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3885506308784941</v>
+        <v>0.6046138257899654</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9677959149531193</v>
+        <v>0.9580647515036661</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>44985</v>
+        <v>40602</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.01173221454357952</v>
+        <v>-0.001181048472159487</v>
       </c>
       <c r="C38" t="n">
-        <v>0.420010256160485</v>
+        <v>0.5664112646979154</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9564415256444895</v>
+        <v>0.9569332305926729</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45016</v>
+        <v>40633</v>
       </c>
       <c r="B39" t="n">
-        <v>0.01949626134347574</v>
+        <v>-0.0008464531803277873</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4667442133175417</v>
+        <v>0.547799537515712</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9750885595882071</v>
+        <v>0.9561232314162763</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45046</v>
+        <v>40663</v>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5</v>
+        <v>0.5508675194776699</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9750885595882071</v>
+        <v>0.9561232314162763</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45077</v>
+        <v>40694</v>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5</v>
+        <v>0.5354730628333793</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9750885595882071</v>
+        <v>0.9561232314162763</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45107</v>
+        <v>40724</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.003973176920485263</v>
+        <v>-0.002548858399203023</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5</v>
+        <v>0.5052958103101779</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9712143602278219</v>
+        <v>0.9536862086872078</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45138</v>
+        <v>40755</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.001328478000507774</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5</v>
+        <v>0.5156404980466823</v>
       </c>
       <c r="D43" t="n">
-        <v>0.969924123316482</v>
+        <v>0.9536862086872078</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45169</v>
+        <v>40786</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.0007972177154135819</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4695692796195139</v>
+        <v>0.5426511158585718</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9691508826227671</v>
+        <v>0.9536862086872078</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45199</v>
+        <v>40816</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>0.01186488891686443</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4633795612213094</v>
+        <v>0.5349035690721223</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9691508826227671</v>
+        <v>0.9650015896148271</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45230</v>
+        <v>40847</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>-0.00826153555444149</v>
       </c>
       <c r="C46" t="n">
-        <v>0.430730029797081</v>
+        <v>0.6296321302801576</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9691508826227671</v>
+        <v>0.9570291946721315</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45260</v>
+        <v>40877</v>
       </c>
       <c r="B47" t="n">
-        <v>0.0232008177232686</v>
+        <v>0.003700655025120401</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4531963259366829</v>
+        <v>0.6241028189005127</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9916359755968427</v>
+        <v>0.9605708295705819</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45291</v>
+        <v>40908</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4679630921291087</v>
+        <v>0.6324740993378906</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9916359755968427</v>
+        <v>0.9605708295705819</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45322</v>
+        <v>40939</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4652496856337715</v>
+        <v>0.6673222075780021</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9916359755968427</v>
+        <v>0.9605708295705819</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45351</v>
+        <v>40968</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.007326050861709562</v>
+        <v>-0.007268195240520305</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4657486620182141</v>
+        <v>0.6674774205954266</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9843712000033192</v>
+        <v>0.9535892132389143</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45382</v>
+        <v>40999</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4590049364668545</v>
+        <v>0.6671401065392919</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9843712000033192</v>
+        <v>0.9535892132389143</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45412</v>
+        <v>41029</v>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0.4245194783747898</v>
+        <v>0.6785951506151374</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9843712000033192</v>
+        <v>0.9535892132389143</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45443</v>
+        <v>41060</v>
       </c>
       <c r="B53" t="n">
-        <v>0.01017232395362883</v>
+        <v>0.01988332550736916</v>
       </c>
       <c r="C53" t="n">
-        <v>0.41696418459088</v>
+        <v>0.6929168804438806</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9943845427403754</v>
+        <v>0.9725497379660597</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45473</v>
+        <v>41090</v>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0.3985505020894868</v>
+        <v>0.7166660604620262</v>
       </c>
       <c r="D54" t="n">
-        <v>0.9943845427403754</v>
+        <v>0.9725497379660597</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45504</v>
+        <v>41121</v>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0.4012781388161359</v>
+        <v>0.6953118298438261</v>
       </c>
       <c r="D55" t="n">
-        <v>0.9943845427403754</v>
+        <v>0.9725497379660597</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45535</v>
+        <v>41152</v>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>-0.0008090985938904452</v>
       </c>
       <c r="C56" t="n">
-        <v>0.4533933511556784</v>
+        <v>0.6896435178339657</v>
       </c>
       <c r="D56" t="n">
-        <v>0.9943845427403754</v>
+        <v>0.9717628493405829</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45565</v>
+        <v>41182</v>
       </c>
       <c r="B57" t="n">
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7120807616959353</v>
+        <v>0.6620214337906931</v>
       </c>
       <c r="D57" t="n">
-        <v>0.9943845427403754</v>
+        <v>0.9717628493405829</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45596</v>
+        <v>41213</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.02306414297885446</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7141977274181817</v>
+        <v>0.6015903123571325</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9714499154706485</v>
+        <v>0.9717628493405829</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45626</v>
+        <v>41243</v>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>0.006297874673913025</v>
       </c>
       <c r="C59" t="n">
-        <v>0.6997953069813579</v>
+        <v>0.650969292273478</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9714499154706485</v>
+        <v>0.9778828899784946</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45657</v>
+        <v>41274</v>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>-0.006032169228495355</v>
       </c>
       <c r="C60" t="n">
-        <v>0.6961599268738149</v>
+        <v>0.6414420706993266</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9714499154706485</v>
+        <v>0.9719841349004942</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45688</v>
+        <v>41305</v>
       </c>
       <c r="B61" t="n">
-        <v>0.004615522468789459</v>
+        <v>-0.008201751970285664</v>
       </c>
       <c r="C61" t="n">
-        <v>0.4185210119778714</v>
+        <v>0.6342579140439093</v>
       </c>
       <c r="D61" t="n">
-        <v>0.9759336643828068</v>
+        <v>0.9640121621069876</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45716</v>
+        <v>41333</v>
       </c>
       <c r="B62" t="n">
-        <v>0.01352009060830633</v>
+        <v>0.007232707303088619</v>
       </c>
       <c r="C62" t="n">
-        <v>0.4152896974132265</v>
+        <v>0.6386050457437602</v>
       </c>
       <c r="D62" t="n">
-        <v>0.9891283759529589</v>
+        <v>0.9709845799121251</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45747</v>
+        <v>41364</v>
       </c>
       <c r="B63" t="n">
-        <v>0.003368248513693574</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.657498557328867</v>
+        <v>0.6815225030894361</v>
       </c>
       <c r="D63" t="n">
-        <v>0.9924600061351146</v>
+        <v>0.9709845799121251</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45777</v>
+        <v>41394</v>
       </c>
       <c r="B64" t="n">
-        <v>0.00638639968383696</v>
+        <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0.4168458048801416</v>
+        <v>0.6746801931038806</v>
       </c>
       <c r="D64" t="n">
-        <v>0.9987982524045167</v>
+        <v>0.9709845799121251</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45808</v>
+        <v>41425</v>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>-0.02097532428477914</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7207185900065797</v>
+        <v>0.6778016902401869</v>
       </c>
       <c r="D65" t="n">
-        <v>0.9987982524045167</v>
+        <v>0.9506178634729482</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45838</v>
+        <v>41455</v>
       </c>
       <c r="B66" t="n">
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7139450190979304</v>
+        <v>0.3893689027987047</v>
       </c>
       <c r="D66" t="n">
-        <v>0.9987982524045167</v>
+        <v>0.9506178634729482</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45869</v>
+        <v>41486</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.002956746801085553</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6862222906548154</v>
+        <v>0.3929746616840607</v>
       </c>
       <c r="D67" t="n">
-        <v>0.9958450588667898</v>
+        <v>0.9506178634729482</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>45900</v>
+        <v>41517</v>
       </c>
       <c r="B68" t="n">
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0.3942727994255228</v>
+        <v>0.4223840726503253</v>
       </c>
       <c r="D68" t="n">
-        <v>0.9958450588667898</v>
+        <v>0.9506178634729482</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>45930</v>
+        <v>41547</v>
       </c>
       <c r="B69" t="n">
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4005524434126393</v>
+        <v>0.4235008845883866</v>
       </c>
       <c r="D69" t="n">
-        <v>0.9958450588667898</v>
+        <v>0.9506178634729482</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>45961</v>
+        <v>41578</v>
       </c>
       <c r="B70" t="n">
-        <v>0.004943744854114182</v>
+        <v>0.003283458915271546</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3978680954788156</v>
+        <v>0.4379220036019602</v>
       </c>
       <c r="D70" t="n">
-        <v>1.000768262752057</v>
+        <v>0.9537391781717848</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>45991</v>
+        <v>41608</v>
       </c>
       <c r="B71" t="n">
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>0.6424619788329925</v>
+        <v>0.4242946840697068</v>
       </c>
       <c r="D71" t="n">
-        <v>1.000768262752057</v>
+        <v>0.9537391781717848</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46022</v>
+        <v>41639</v>
       </c>
       <c r="B72" t="n">
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6334091619355577</v>
+        <v>0.4350962956665848</v>
       </c>
       <c r="D72" t="n">
-        <v>1.000768262752057</v>
+        <v>0.9537391781717848</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46053</v>
+        <v>41670</v>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>0.0131377597549581</v>
       </c>
       <c r="C73" t="n">
-        <v>0.6361187959231078</v>
+        <v>0.4288812383238805</v>
       </c>
       <c r="D73" t="n">
-        <v>1.000768262752057</v>
+        <v>0.9662691743634968</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46081</v>
+        <v>41698</v>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>0.001733212511516683</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6058268087631197</v>
+        <v>0.4512097574845144</v>
       </c>
       <c r="D74" t="n">
-        <v>1.000768262752057</v>
+        <v>0.9679439241859964</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46112</v>
+        <v>41729</v>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>-0.00240198454768155</v>
       </c>
       <c r="C75" t="n">
-        <v>0.5944497786901271</v>
+        <v>0.4048857826981662</v>
       </c>
       <c r="D75" t="n">
-        <v>1.000768262752057</v>
+        <v>0.9656189378370793</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
+        <v>41759</v>
+      </c>
+      <c r="B76" t="n">
+        <v>0.00310014003409512</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.4088001399228535</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.9686124917639484</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>41790</v>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.3794424564646061</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.9686124917639484</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>41820</v>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.6374013952512927</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.9686124917639484</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>41851</v>
+      </c>
+      <c r="B79" t="n">
+        <v>-0.001443532101157134</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.6163907467029692</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.9672142685385053</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>41882</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.6528510828644036</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.9672142685385053</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>41912</v>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.6695357704942346</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.9672142685385053</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>41943</v>
+      </c>
+      <c r="B82" t="n">
+        <v>0.01044396537287548</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.6843222114082317</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.9773158208672725</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>41973</v>
+      </c>
+      <c r="B83" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.6981844955700232</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.9773158208672725</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>42004</v>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.734970874027373</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.9773158208672725</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>42035</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.9773158208672725</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>42063</v>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.9773158208672725</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>42094</v>
+      </c>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.9773158208672725</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>42124</v>
+      </c>
+      <c r="B88" t="n">
+        <v>-0.004802601331703121</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.9726221626044809</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>42155</v>
+      </c>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.9726221626044809</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>42185</v>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.9726221626044809</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>42216</v>
+      </c>
+      <c r="B91" t="n">
+        <v>0.01138842967573908</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.9836988017043673</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>42247</v>
+      </c>
+      <c r="B92" t="n">
+        <v>0.0005921063045743521</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.9842812559666587</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>42277</v>
+      </c>
+      <c r="B93" t="n">
+        <v>0.01173469284960414</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.9958314941830499</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>42308</v>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.9958314941830499</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>42338</v>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.9958314941830499</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>42369</v>
+      </c>
+      <c r="B96" t="n">
+        <v>-0.003452550868136706</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.9923933352932904</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>42400</v>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.7408831202765281</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.9923933352932904</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>42429</v>
+      </c>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.7390068787452939</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.9923933352932904</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>42460</v>
+      </c>
+      <c r="B99" t="n">
+        <v>-0.000494759039296245</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.748504536406205</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.9919023397201167</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>42490</v>
+      </c>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.7225678879278936</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.9919023397201167</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>42521</v>
+      </c>
+      <c r="B101" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.7061375018104719</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.9919023397201167</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>42551</v>
+      </c>
+      <c r="B102" t="n">
+        <v>0.02135952928593573</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.6939583865083663</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1.013088906794157</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>42582</v>
+      </c>
+      <c r="B103" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.6736557390639467</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1.013088906794157</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>42613</v>
+      </c>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.6529891677420345</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1.013088906794157</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>42643</v>
+      </c>
+      <c r="B105" t="n">
+        <v>0.001592449331722631</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.637275727248381</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1.014702199546756</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>42674</v>
+      </c>
+      <c r="B106" t="n">
+        <v>-0.009080528480864585</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.6131806423941479</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1.005488167324176</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>42704</v>
+      </c>
+      <c r="B107" t="n">
+        <v>-0.02611932080934504</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.6138817503925622</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.9792254993118357</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>42735</v>
+      </c>
+      <c r="B108" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.5689416649904263</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.9792254993118357</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>42766</v>
+      </c>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.5149446991891804</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.9792254993118357</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>42794</v>
+      </c>
+      <c r="B110" t="n">
+        <v>0.002186293734793916</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.9813663738859315</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>42825</v>
+      </c>
+      <c r="B111" t="n">
+        <v>7.019741151982956e-05</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.9814352632651309</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>42855</v>
+      </c>
+      <c r="B112" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.2751967050658766</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.9814352632651309</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>42886</v>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.3563918777519264</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.9814352632651309</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>42916</v>
+      </c>
+      <c r="B114" t="n">
+        <v>-0.001253776971611931</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.3726869533742163</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.9802047623329212</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>42947</v>
+      </c>
+      <c r="B115" t="n">
+        <v>0.001689417296148682</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.3981428719901088</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.9818607372121736</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>42978</v>
+      </c>
+      <c r="B116" t="n">
+        <v>0.005547705173328987</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.328151663710693</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.9873078111034942</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>43008</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.333738075286623</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.9873078111034942</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>43039</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.351354038113854</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.9873078111034942</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>43069</v>
+      </c>
+      <c r="B119" t="n">
+        <v>-0.0005617104852906587</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.3319429591957537</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.986753229953788</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>43100</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5931088090577288</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.986753229953788</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>43131</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.5905642343383459</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.986753229953788</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>43159</v>
+      </c>
+      <c r="B122" t="n">
+        <v>-0.002499461098858688</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.3278758784485775</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.9842868786413453</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>43190</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.3396275610021233</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.9842868786413453</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>43220</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.3056623277389066</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.9842868786413453</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>43251</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.003779222963620791</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.2727107200733095</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.9880067182158975</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>43281</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.9880067182158975</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>43312</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.2544203946561677</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.9880067182158975</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>43343</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.004046626734571212</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.2876644705588225</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.9920048126157658</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>43373</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.2935745730149633</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.9920048126157658</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>43404</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.2851205371088266</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.9920048126157658</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>43434</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.005762325788958567</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3410944909670695</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.9977210675302726</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>43465</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.01239928936753396</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4032755438191494</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1.010092099754665</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>43496</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.003808907928235797</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.4312107029686896</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.013939447561669</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>43524</v>
+      </c>
+      <c r="B134" t="n">
+        <v>-0.002857504086753399</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.66247557356189</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1.011042111446541</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>43555</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.6339857007555003</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.011042111446541</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>43585</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.6471852535523843</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1.011042111446541</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>43616</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.0207788993601413</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.6577623753079959</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.032050453729153</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>43646</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.6986694273727787</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.032050453729153</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>43677</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.6659212044949752</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1.032050453729153</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>43708</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.6649211322262742</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1.032050453729153</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>43738</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.6900938646258732</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1.032050453729153</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>43769</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.001797372283239479</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.6991173582023383</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.033905432609591</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>43799</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6626498831253183</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1.033905432609591</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>43830</v>
+      </c>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.6122508473075328</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1.033905432609591</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="B145" t="n">
+        <v>0.01979272997693522</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.5556648370960907</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1.054369243658919</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="B146" t="n">
+        <v>0</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.6470069482253763</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1.054369243658919</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>43921</v>
+      </c>
+      <c r="B147" t="n">
+        <v>0</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0.6844897865523523</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1.054369243658919</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>43951</v>
+      </c>
+      <c r="B148" t="n">
+        <v>0.002015431617686713</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1.056494252769306</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>43982</v>
+      </c>
+      <c r="B149" t="n">
+        <v>0</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1.056494252769306</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>44012</v>
+      </c>
+      <c r="B150" t="n">
+        <v>0</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0.7279529523593287</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1.056494252769306</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>44043</v>
+      </c>
+      <c r="B151" t="n">
+        <v>0.006160745483707937</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.7176908611847685</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1.063003044965618</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>44074</v>
+      </c>
+      <c r="B152" t="n">
+        <v>-0.006644783999891854</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0.6851226232498039</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1.055939619340594</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>44104</v>
+      </c>
+      <c r="B153" t="n">
+        <v>0.002054420722007326</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0.6500427723137689</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1.058108963575755</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>44135</v>
+      </c>
+      <c r="B154" t="n">
+        <v>0</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0.6728531011285326</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1.058108963575755</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>44165</v>
+      </c>
+      <c r="B155" t="n">
+        <v>0</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0.709301542916468</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1.058108963575755</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>44196</v>
+      </c>
+      <c r="B156" t="n">
+        <v>-0.001545053446064514</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0.6526830972900506</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1.056474128675271</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>44227</v>
+      </c>
+      <c r="B157" t="n">
+        <v>0</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0.6617150404618696</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1.056474128675271</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>44255</v>
+      </c>
+      <c r="B158" t="n">
+        <v>0</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0.5889642298494011</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1.056474128675271</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>44286</v>
+      </c>
+      <c r="B159" t="n">
+        <v>0</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1.056474128675271</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>44316</v>
+      </c>
+      <c r="B160" t="n">
+        <v>0.002503088152636117</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1.059118576550325</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>44347</v>
+      </c>
+      <c r="B161" t="n">
+        <v>0</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1.059118576550325</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>44377</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1.059118576550325</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>44408</v>
+      </c>
+      <c r="B163" t="n">
+        <v>0</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1.059118576550325</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="B164" t="n">
+        <v>0</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1.059118576550325</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="B165" t="n">
+        <v>-0.003910300542024788</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1.054977104606372</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="B166" t="n">
+        <v>0</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1.054977104606372</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="B167" t="n">
+        <v>0</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1.054977104606372</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B168" t="n">
+        <v>-0.00131010677760402</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1.05359497195141</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>44592</v>
+      </c>
+      <c r="B169" t="n">
+        <v>-0.005282550721885088</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1.048029303071753</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>44620</v>
+      </c>
+      <c r="B170" t="n">
+        <v>-0.0009240939217473971</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1.047060825562972</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>44651</v>
+      </c>
+      <c r="B171" t="n">
+        <v>-0.00980777203045274</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1.036791491683832</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>44681</v>
+      </c>
+      <c r="B172" t="n">
+        <v>0</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1.036791491683832</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>44712</v>
+      </c>
+      <c r="B173" t="n">
+        <v>0</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1.036791491683832</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>44742</v>
+      </c>
+      <c r="B174" t="n">
+        <v>-0.001575980491778945</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1.035157528518896</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>44773</v>
+      </c>
+      <c r="B175" t="n">
+        <v>0</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1.035157528518896</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>44804</v>
+      </c>
+      <c r="B176" t="n">
+        <v>0</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1.035157528518896</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>44834</v>
+      </c>
+      <c r="B177" t="n">
+        <v>-0.01028642585360674</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1.024509457354984</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>44865</v>
+      </c>
+      <c r="B178" t="n">
+        <v>-0.003417467469062724</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.3102500001706751</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1.021008229612726</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>44895</v>
+      </c>
+      <c r="B179" t="n">
+        <v>0.01340966879267804</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0.3111204895355094</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1.034699611806431</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>44926</v>
+      </c>
+      <c r="B180" t="n">
+        <v>0</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1.034699611806431</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>44957</v>
+      </c>
+      <c r="B181" t="n">
+        <v>0</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.3001305969526212</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1.034699611806431</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>44985</v>
+      </c>
+      <c r="B182" t="n">
+        <v>-0.008723426129002331</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.3368091565432284</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1.025673486177131</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B183" t="n">
+        <v>0.01697728530554002</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0.3909209124506307</v>
+      </c>
+      <c r="D183" t="n">
+        <v>1.043086637582288</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>45046</v>
+      </c>
+      <c r="B184" t="n">
+        <v>0</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.431010561502662</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1.043086637582288</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>45077</v>
+      </c>
+      <c r="B185" t="n">
+        <v>0</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.4602065609884485</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1.043086637582288</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B186" t="n">
+        <v>-0.003969709809855467</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.4998032086429878</v>
+      </c>
+      <c r="D186" t="n">
+        <v>1.038945886324548</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>45138</v>
+      </c>
+      <c r="B187" t="n">
+        <v>-0.0008911023993022241</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0.4578656922294118</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1.038020079152499</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>45169</v>
+      </c>
+      <c r="B188" t="n">
+        <v>-0.0001034496172266546</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0.4130379587464973</v>
+      </c>
+      <c r="D188" t="n">
+        <v>1.037912696372637</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>45199</v>
+      </c>
+      <c r="B189" t="n">
+        <v>0</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.4077369679552783</v>
+      </c>
+      <c r="D189" t="n">
+        <v>1.037912696372637</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>45230</v>
+      </c>
+      <c r="B190" t="n">
+        <v>0</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.3716645489708902</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1.037912696372637</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="B191" t="n">
+        <v>0.02095692533356018</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.39828572864997</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1.059664155253273</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>45291</v>
+      </c>
+      <c r="B192" t="n">
+        <v>0</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0.4164248757325223</v>
+      </c>
+      <c r="D192" t="n">
+        <v>1.059664155253273</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>45322</v>
+      </c>
+      <c r="B193" t="n">
+        <v>0</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0.4149465510916716</v>
+      </c>
+      <c r="D193" t="n">
+        <v>1.059664155253273</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="B194" t="n">
+        <v>-0.006094406739692357</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0.4170077940065325</v>
+      </c>
+      <c r="D194" t="n">
+        <v>1.053206130883687</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B195" t="n">
+        <v>0</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.4108347904686717</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1.053206130883687</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>45412</v>
+      </c>
+      <c r="B196" t="n">
+        <v>0</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.3731656502250368</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1.053206130883687</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>45443</v>
+      </c>
+      <c r="B197" t="n">
+        <v>0.009478535051071395</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0.3653139762978134</v>
+      </c>
+      <c r="D197" t="n">
+        <v>1.063188982111271</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>45473</v>
+      </c>
+      <c r="B198" t="n">
+        <v>0</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0.3452966387000535</v>
+      </c>
+      <c r="D198" t="n">
+        <v>1.063188982111271</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>45504</v>
+      </c>
+      <c r="B199" t="n">
+        <v>0</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0.3486483129332825</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1.063188982111271</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>45535</v>
+      </c>
+      <c r="B200" t="n">
+        <v>0</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0.4063301478433092</v>
+      </c>
+      <c r="D200" t="n">
+        <v>1.063188982111271</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B201" t="n">
+        <v>0</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0.6668517415603471</v>
+      </c>
+      <c r="D201" t="n">
+        <v>1.063188982111271</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>45596</v>
+      </c>
+      <c r="B202" t="n">
+        <v>-0.02140391479422332</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0.6703036750058322</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1.040432575728004</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>45626</v>
+      </c>
+      <c r="B203" t="n">
+        <v>0</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0.6557384519672884</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1.040432575728004</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>45657</v>
+      </c>
+      <c r="B204" t="n">
+        <v>0</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0.6526485150819625</v>
+      </c>
+      <c r="D204" t="n">
+        <v>1.040432575728004</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B205" t="n">
+        <v>0.004495662980923064</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0.373483049335197</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1.045110009942851</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B206" t="n">
+        <v>0.01240927195260916</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.3704364135738338</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1.058079064276626</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="B207" t="n">
+        <v>0.003361775607643689</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0.6124763537918628</v>
+      </c>
+      <c r="D207" t="n">
+        <v>1.06163608866587</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B208" t="n">
+        <v>0.00607095047253387</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0.3727766257451262</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1.068081228780015</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B209" t="n">
+        <v>0</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.6803828556420777</v>
+      </c>
+      <c r="D209" t="n">
+        <v>1.068081228780015</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B210" t="n">
+        <v>0</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0.6742897748903307</v>
+      </c>
+      <c r="D210" t="n">
+        <v>1.068081228780015</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B211" t="n">
+        <v>-0.00257344253468376</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0.6458931195776387</v>
+      </c>
+      <c r="D211" t="n">
+        <v>1.065332583115375</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B212" t="n">
+        <v>0</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0.352199534136267</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1.065332583115375</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B213" t="n">
+        <v>0</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0.3589970463410664</v>
+      </c>
+      <c r="D213" t="n">
+        <v>1.065332583115375</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B214" t="n">
+        <v>0.004794486641753321</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0.3564345375402613</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1.070440305954146</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B215" t="n">
+        <v>0</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.6010373223671923</v>
+      </c>
+      <c r="D215" t="n">
+        <v>1.070440305954146</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B216" t="n">
+        <v>0</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0.5918640725587734</v>
+      </c>
+      <c r="D216" t="n">
+        <v>1.070440305954146</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B217" t="n">
+        <v>0</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0.5947948426930394</v>
+      </c>
+      <c r="D217" t="n">
+        <v>1.070440305954146</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B218" t="n">
+        <v>0</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0.5639298629423446</v>
+      </c>
+      <c r="D218" t="n">
+        <v>1.070440305954146</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B219" t="n">
+        <v>0</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0.5523774415163224</v>
+      </c>
+      <c r="D219" t="n">
+        <v>1.070440305954146</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="B76" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" t="n">
-        <v>0.2640762179753054</v>
-      </c>
-      <c r="D76" t="n">
-        <v>1.000768262752057</v>
+      <c r="B220" t="n">
+        <v>0</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D220" t="n">
+        <v>1.070440305954146</v>
       </c>
     </row>
   </sheetData>

--- a/ptr_equity.xlsx
+++ b/ptr_equity.xlsx
@@ -447,13 +447,13 @@
         <v>39507</v>
       </c>
       <c r="B2" t="n">
-        <v>0.007014036987233432</v>
+        <v>0.007014345521468</v>
       </c>
       <c r="C2" t="n">
         <v>0.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.007014036987233</v>
+        <v>1.007014345521468</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +461,13 @@
         <v>39538</v>
       </c>
       <c r="B3" t="n">
-        <v>0.007853313135982663</v>
+        <v>0.007853907577004809</v>
       </c>
       <c r="C3" t="n">
         <v>0.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.014922433552024</v>
+        <v>1.014923343119912</v>
       </c>
     </row>
     <row r="4">
@@ -475,13 +475,13 @@
         <v>39568</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.01241396782531058</v>
+        <v>-0.01241398086991757</v>
       </c>
       <c r="C4" t="n">
         <v>0.5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.002323219116723</v>
+        <v>1.002324104153988</v>
       </c>
     </row>
     <row r="5">
@@ -489,13 +489,13 @@
         <v>39599</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-0.005084766911878444</v>
       </c>
       <c r="C5" t="n">
         <v>0.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.002323219116723</v>
+        <v>0.997227519714208</v>
       </c>
     </row>
     <row r="6">
@@ -503,13 +503,13 @@
         <v>39629</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.004001125991351063</v>
       </c>
       <c r="C6" t="n">
         <v>0.625</v>
       </c>
       <c r="D6" t="n">
-        <v>1.002323219116723</v>
+        <v>1.001217552662627</v>
       </c>
     </row>
     <row r="7">
@@ -517,13 +517,13 @@
         <v>39660</v>
       </c>
       <c r="B7" t="n">
-        <v>0.005206621403512517</v>
+        <v>0.005207152762370058</v>
       </c>
       <c r="C7" t="n">
         <v>0.625</v>
       </c>
       <c r="D7" t="n">
-        <v>1.007541936642614</v>
+        <v>1.006431045407708</v>
       </c>
     </row>
     <row r="8">
@@ -531,13 +531,13 @@
         <v>39691</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.01356013046290881</v>
       </c>
       <c r="C8" t="n">
         <v>0.625</v>
       </c>
       <c r="D8" t="n">
-        <v>1.007541936642614</v>
+        <v>1.020078381685358</v>
       </c>
     </row>
     <row r="9">
@@ -545,13 +545,13 @@
         <v>39721</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-0.002620999999126942</v>
       </c>
       <c r="C9" t="n">
         <v>0.625</v>
       </c>
       <c r="D9" t="n">
-        <v>1.007541936642614</v>
+        <v>1.017404756247851</v>
       </c>
     </row>
     <row r="10">
@@ -559,13 +559,13 @@
         <v>39752</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.006265065059176272</v>
+        <v>-0.00626497949441163</v>
       </c>
       <c r="C10" t="n">
         <v>0.625</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0012296208597</v>
+        <v>1.011030736312442</v>
       </c>
     </row>
     <row r="11">
@@ -573,13 +573,13 @@
         <v>39782</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.05841979049370742</v>
       </c>
       <c r="C11" t="n">
         <v>0.625</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0012296208597</v>
+        <v>1.070094940110513</v>
       </c>
     </row>
     <row r="12">
@@ -587,13 +587,13 @@
         <v>39813</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.02253427966490397</v>
       </c>
       <c r="C12" t="n">
         <v>0.625</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0012296208597</v>
+        <v>1.094208758758962</v>
       </c>
     </row>
     <row r="13">
@@ -601,13 +601,13 @@
         <v>39844</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-0.01845590045314321</v>
       </c>
       <c r="C13" t="n">
         <v>0.625</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0012296208597</v>
+        <v>1.074014150832349</v>
       </c>
     </row>
     <row r="14">
@@ -615,13 +615,13 @@
         <v>39872</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0.003435264091435392</v>
       </c>
       <c r="C14" t="n">
         <v>0.625</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0012296208597</v>
+        <v>1.070324628586302</v>
       </c>
     </row>
     <row r="15">
@@ -629,13 +629,13 @@
         <v>39903</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.01405119557629203</v>
       </c>
       <c r="C15" t="n">
         <v>0.625</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0012296208597</v>
+        <v>1.08536396927269</v>
       </c>
     </row>
     <row r="16">
@@ -643,13 +643,13 @@
         <v>39933</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.0169283794220732</v>
+        <v>-0.0169285185759702</v>
       </c>
       <c r="C16" t="n">
         <v>0.625</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9842804259491681</v>
+        <v>1.066990365157168</v>
       </c>
     </row>
     <row r="17">
@@ -657,13 +657,13 @@
         <v>39964</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>-0.02322437176089449</v>
       </c>
       <c r="C17" t="n">
         <v>0.625</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9842804259491681</v>
+        <v>1.042210184251465</v>
       </c>
     </row>
     <row r="18">
@@ -671,13 +671,13 @@
         <v>39994</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.007074786275549852</v>
       </c>
       <c r="C18" t="n">
         <v>0.625</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9842804259491681</v>
+        <v>1.049583598559246</v>
       </c>
     </row>
     <row r="19">
@@ -685,13 +685,13 @@
         <v>40025</v>
       </c>
       <c r="B19" t="n">
-        <v>0.004961852745142949</v>
+        <v>0.00496002903218457</v>
       </c>
       <c r="C19" t="n">
         <v>0.625</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9891642804826545</v>
+        <v>1.054789563679805</v>
       </c>
     </row>
     <row r="20">
@@ -699,13 +699,13 @@
         <v>40056</v>
       </c>
       <c r="B20" t="n">
-        <v>0.005032885895329139</v>
+        <v>0.005033545021587742</v>
       </c>
       <c r="C20" t="n">
         <v>0.625</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9941426314380591</v>
+        <v>1.060098894436888</v>
       </c>
     </row>
     <row r="21">
@@ -713,13 +713,13 @@
         <v>40086</v>
       </c>
       <c r="B21" t="n">
-        <v>0.007125589171385832</v>
+        <v>0.007125402800317999</v>
       </c>
       <c r="C21" t="n">
         <v>0.625</v>
       </c>
       <c r="D21" t="n">
-        <v>1.001226483407447</v>
+        <v>1.067652526067922</v>
       </c>
     </row>
     <row r="22">
@@ -727,13 +727,13 @@
         <v>40117</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>-0.002479061286954358</v>
       </c>
       <c r="C22" t="n">
         <v>0.625</v>
       </c>
       <c r="D22" t="n">
-        <v>1.001226483407447</v>
+        <v>1.065005750022628</v>
       </c>
     </row>
     <row r="23">
@@ -741,13 +741,13 @@
         <v>40147</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>0.01412532091597229</v>
       </c>
       <c r="C23" t="n">
         <v>0.625</v>
       </c>
       <c r="D23" t="n">
-        <v>1.001226483407447</v>
+        <v>1.080049298019053</v>
       </c>
     </row>
     <row r="24">
@@ -755,13 +755,13 @@
         <v>40178</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.02740258534306548</v>
+        <v>-0.02740312196062204</v>
       </c>
       <c r="C24" t="n">
         <v>0.625</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9737902892481372</v>
+        <v>1.050452575381953</v>
       </c>
     </row>
     <row r="25">
@@ -769,13 +769,13 @@
         <v>40209</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>0.007435710497891156</v>
       </c>
       <c r="C25" t="n">
         <v>0.375</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9737902892481372</v>
+        <v>1.058263436624257</v>
       </c>
     </row>
     <row r="26">
@@ -783,13 +783,13 @@
         <v>40237</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>0.002659104778533958</v>
       </c>
       <c r="C26" t="n">
         <v>0.375</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9737902892481372</v>
+        <v>1.061077469985533</v>
       </c>
     </row>
     <row r="27">
@@ -797,13 +797,13 @@
         <v>40268</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>-0.007083691867136746</v>
       </c>
       <c r="C27" t="n">
         <v>0.625</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9737902892481372</v>
+        <v>1.053561124140994</v>
       </c>
     </row>
     <row r="28">
@@ -811,13 +811,13 @@
         <v>40298</v>
       </c>
       <c r="B28" t="n">
-        <v>0.00592475484501152</v>
+        <v>0.005925163684068941</v>
       </c>
       <c r="C28" t="n">
         <v>0.375</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9795597579823851</v>
+        <v>1.059803646252701</v>
       </c>
     </row>
     <row r="29">
@@ -825,13 +825,13 @@
         <v>40329</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.01932787495507193</v>
       </c>
       <c r="C29" t="n">
         <v>0.625</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9795597579823851</v>
+        <v>1.080287398604403</v>
       </c>
     </row>
     <row r="30">
@@ -839,13 +839,13 @@
         <v>40359</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.01830197595193438</v>
       </c>
       <c r="C30" t="n">
         <v>0.625</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9795597579823851</v>
+        <v>1.100058792594838</v>
       </c>
     </row>
     <row r="31">
@@ -853,13 +853,13 @@
         <v>40390</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.003489674205004358</v>
       </c>
       <c r="C31" t="n">
         <v>0.625</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9795597579823851</v>
+        <v>1.103897639387345</v>
       </c>
     </row>
     <row r="32">
@@ -867,13 +867,13 @@
         <v>40421</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>0.02350057097143307</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6370460448606655</v>
+        <v>0.6370460603010593</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9795597579823851</v>
+        <v>1.129839864206964</v>
       </c>
     </row>
     <row r="33">
@@ -881,13 +881,13 @@
         <v>40451</v>
       </c>
       <c r="B33" t="n">
-        <v>-1.913591707205205e-05</v>
+        <v>-1.879543101280775e-05</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6283573921782999</v>
+        <v>0.6283574089230504</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9795410132080893</v>
+        <v>1.129818628379741</v>
       </c>
     </row>
     <row r="34">
@@ -895,13 +895,13 @@
         <v>40482</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>-0.0009633769093232093</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6019420669213249</v>
+        <v>0.6019420171494322</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9795410132080893</v>
+        <v>1.128730187201437</v>
       </c>
     </row>
     <row r="35">
@@ -909,13 +909,13 @@
         <v>40512</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>-0.004488391427368039</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6131522648752805</v>
+        <v>0.6131523201848678</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9795410132080893</v>
+        <v>1.12366400430539</v>
       </c>
     </row>
     <row r="36">
@@ -923,13 +923,13 @@
         <v>40543</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.02179889272121318</v>
+        <v>-0.02179909886455179</v>
       </c>
       <c r="C36" t="n">
-        <v>0.633041522104832</v>
+        <v>0.633041476464943</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9581881037451377</v>
+        <v>1.099169141584999</v>
       </c>
     </row>
     <row r="37">
@@ -937,13 +937,13 @@
         <v>40574</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.0001287348913950908</v>
+        <v>-0.0001290088369963991</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6046138257899654</v>
+        <v>0.6046138152173345</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9580647515036661</v>
+        <v>1.099027339052381</v>
       </c>
     </row>
     <row r="38">
@@ -951,13 +951,13 @@
         <v>40602</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.001181048472159487</v>
+        <v>-0.00118021557425139</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5664112646979154</v>
+        <v>0.566411401630172</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9569332305926729</v>
+        <v>1.097730249870303</v>
       </c>
     </row>
     <row r="39">
@@ -965,13 +965,13 @@
         <v>40633</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.0008464531803277873</v>
+        <v>-0.0008470744928424231</v>
       </c>
       <c r="C39" t="n">
-        <v>0.547799537515712</v>
+        <v>0.5477995673268479</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9561232314162763</v>
+        <v>1.096800390575617</v>
       </c>
     </row>
     <row r="40">
@@ -979,13 +979,13 @@
         <v>40663</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>0.009970603051073829</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5508675194776699</v>
+        <v>0.5508676141183134</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9561232314162763</v>
+        <v>1.107736151896309</v>
       </c>
     </row>
     <row r="41">
@@ -993,13 +993,13 @@
         <v>40694</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>0.01368741989072231</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5354730628333793</v>
+        <v>0.5354731141758632</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9561232314162763</v>
+        <v>1.122898201735447</v>
       </c>
     </row>
     <row r="42">
@@ -1007,13 +1007,13 @@
         <v>40724</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.002548858399203023</v>
+        <v>-0.002549352150882555</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5052958103101779</v>
+        <v>0.5052958932804609</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9536862086872078</v>
+        <v>1.12003553878963</v>
       </c>
     </row>
     <row r="43">
@@ -1021,13 +1021,13 @@
         <v>40755</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>0.01827865471838107</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5156404980466823</v>
+        <v>0.5156405628797637</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9536862086872078</v>
+        <v>1.140508281675482</v>
       </c>
     </row>
     <row r="44">
@@ -1035,13 +1035,13 @@
         <v>40786</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>0.023182405073955</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5426511158585718</v>
+        <v>0.5426511014687702</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9536862086872078</v>
+        <v>1.166948006651483</v>
       </c>
     </row>
     <row r="45">
@@ -1049,13 +1049,13 @@
         <v>40816</v>
       </c>
       <c r="B45" t="n">
-        <v>0.01186488891686443</v>
+        <v>0.011864665766143</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5349035690721223</v>
+        <v>0.5349035075024264</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9650015896148271</v>
+        <v>1.18079345471687</v>
       </c>
     </row>
     <row r="46">
@@ -1063,13 +1063,13 @@
         <v>40847</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.00826153555444149</v>
+        <v>-0.00826211447433369</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6296321302801576</v>
+        <v>0.6296321797172768</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9570291946721315</v>
+        <v>1.171037604023455</v>
       </c>
     </row>
     <row r="47">
@@ -1077,13 +1077,13 @@
         <v>40877</v>
       </c>
       <c r="B47" t="n">
-        <v>0.003700655025120401</v>
+        <v>0.00370121637806323</v>
       </c>
       <c r="C47" t="n">
-        <v>0.6241028189005127</v>
+        <v>0.6241027956737921</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9605708295705819</v>
+        <v>1.175371867582795</v>
       </c>
     </row>
     <row r="48">
@@ -1091,13 +1091,13 @@
         <v>40908</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>0.008333173819447199</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6324740993378906</v>
+        <v>0.6324741132617607</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9605708295705819</v>
+        <v>1.18516644565785</v>
       </c>
     </row>
     <row r="49">
@@ -1105,13 +1105,13 @@
         <v>40939</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>0.01005137196928763</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6673222075780021</v>
+        <v>0.6673222457637054</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9605708295705819</v>
+        <v>1.197078994448676</v>
       </c>
     </row>
     <row r="50">
@@ -1119,13 +1119,13 @@
         <v>40968</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.007268195240520305</v>
+        <v>-0.007268951486723866</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6674774205954266</v>
+        <v>0.6674773685013917</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9535892132389143</v>
+        <v>1.188377485312252</v>
       </c>
     </row>
     <row r="51">
@@ -1133,13 +1133,13 @@
         <v>40999</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>-0.009188109411224152</v>
       </c>
       <c r="C51" t="n">
-        <v>0.6671401065392919</v>
+        <v>0.667140057247005</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9535892132389143</v>
+        <v>1.177458542955368</v>
       </c>
     </row>
     <row r="52">
@@ -1147,13 +1147,13 @@
         <v>41029</v>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>0.01550484036499829</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6785951506151374</v>
+        <v>0.6785951847101059</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9535892132389143</v>
+        <v>1.195714849700294</v>
       </c>
     </row>
     <row r="53">
@@ -1161,13 +1161,13 @@
         <v>41060</v>
       </c>
       <c r="B53" t="n">
-        <v>0.01988332550736916</v>
+        <v>0.01988319423987513</v>
       </c>
       <c r="C53" t="n">
-        <v>0.6929168804438806</v>
+        <v>0.6929169384552474</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9725497379660597</v>
+        <v>1.219489480312388</v>
       </c>
     </row>
     <row r="54">
@@ -1175,13 +1175,13 @@
         <v>41090</v>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>0.0002189085054803417</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7166660604620262</v>
+        <v>0.7166661148796795</v>
       </c>
       <c r="D54" t="n">
-        <v>0.9725497379660597</v>
+        <v>1.219756436931972</v>
       </c>
     </row>
     <row r="55">
@@ -1189,13 +1189,13 @@
         <v>41121</v>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>0.00648627322819099</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6953118298438261</v>
+        <v>0.6953118032967599</v>
       </c>
       <c r="D55" t="n">
-        <v>0.9725497379660597</v>
+        <v>1.227668110453758</v>
       </c>
     </row>
     <row r="56">
@@ -1203,13 +1203,13 @@
         <v>41152</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.0008090985938904452</v>
+        <v>-0.0008094862064321114</v>
       </c>
       <c r="C56" t="n">
-        <v>0.6896435178339657</v>
+        <v>0.6896435470869868</v>
       </c>
       <c r="D56" t="n">
-        <v>0.9717628493405829</v>
+        <v>1.226674330052269</v>
       </c>
     </row>
     <row r="57">
@@ -1217,13 +1217,13 @@
         <v>41182</v>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>-0.001080499702332674</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6620214337906931</v>
+        <v>0.6620213790239634</v>
       </c>
       <c r="D57" t="n">
-        <v>0.9717628493405829</v>
+        <v>1.225348908803788</v>
       </c>
     </row>
     <row r="58">
@@ -1231,13 +1231,13 @@
         <v>41213</v>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>-0.003405569162135986</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6015903123571325</v>
+        <v>0.6015903272059189</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9717628493405829</v>
+        <v>1.221175898347109</v>
       </c>
     </row>
     <row r="59">
@@ -1245,13 +1245,13 @@
         <v>41243</v>
       </c>
       <c r="B59" t="n">
-        <v>0.006297874673913025</v>
+        <v>0.006297614753211236</v>
       </c>
       <c r="C59" t="n">
-        <v>0.650969292273478</v>
+        <v>0.6509693336862098</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9778828899784946</v>
+        <v>1.228866393700806</v>
       </c>
     </row>
     <row r="60">
@@ -1259,13 +1259,13 @@
         <v>41274</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.006032169228495355</v>
+        <v>-0.006031693937194302</v>
       </c>
       <c r="C60" t="n">
-        <v>0.6414420706993266</v>
+        <v>0.6414421136645678</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9719841349004942</v>
+        <v>1.221454247724299</v>
       </c>
     </row>
     <row r="61">
@@ -1273,13 +1273,13 @@
         <v>41305</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.008201751970285664</v>
+        <v>-0.008201931837437731</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6342579140439093</v>
+        <v>0.634257922901684</v>
       </c>
       <c r="D61" t="n">
-        <v>0.9640121621069876</v>
+        <v>1.211435963241916</v>
       </c>
     </row>
     <row r="62">
@@ -1287,13 +1287,13 @@
         <v>41333</v>
       </c>
       <c r="B62" t="n">
-        <v>0.007232707303088619</v>
+        <v>0.007232830547287488</v>
       </c>
       <c r="C62" t="n">
-        <v>0.6386050457437602</v>
+        <v>0.6386049513086152</v>
       </c>
       <c r="D62" t="n">
-        <v>0.9709845799121251</v>
+        <v>1.220198074282934</v>
       </c>
     </row>
     <row r="63">
@@ -1301,13 +1301,13 @@
         <v>41364</v>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>0.00370223804236951</v>
       </c>
       <c r="C63" t="n">
-        <v>0.6815225030894361</v>
+        <v>0.6815225395634061</v>
       </c>
       <c r="D63" t="n">
-        <v>0.9709845799121251</v>
+        <v>1.224715538012771</v>
       </c>
     </row>
     <row r="64">
@@ -1315,13 +1315,13 @@
         <v>41394</v>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>0.008474390756865787</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6746801931038806</v>
+        <v>0.6746802302946591</v>
       </c>
       <c r="D64" t="n">
-        <v>0.9709845799121251</v>
+        <v>1.235094256047896</v>
       </c>
     </row>
     <row r="65">
@@ -1329,13 +1329,13 @@
         <v>41425</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.02097532428477914</v>
+        <v>-0.02097545510577544</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6778016902401869</v>
+        <v>0.6778016587598625</v>
       </c>
       <c r="D65" t="n">
-        <v>0.9506178634729482</v>
+        <v>1.209187591928762</v>
       </c>
     </row>
     <row r="66">
@@ -1343,13 +1343,13 @@
         <v>41455</v>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>-0.009769774441362756</v>
       </c>
       <c r="C66" t="n">
-        <v>0.3893689027987047</v>
+        <v>0.3893689104224929</v>
       </c>
       <c r="D66" t="n">
-        <v>0.9506178634729482</v>
+        <v>1.197374101898323</v>
       </c>
     </row>
     <row r="67">
@@ -1357,13 +1357,13 @@
         <v>41486</v>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>-0.001666919643609012</v>
       </c>
       <c r="C67" t="n">
-        <v>0.3929746616840607</v>
+        <v>0.3929746301061067</v>
       </c>
       <c r="D67" t="n">
-        <v>0.9506178634729482</v>
+        <v>1.19537817548712</v>
       </c>
     </row>
     <row r="68">
@@ -1371,13 +1371,13 @@
         <v>41517</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>-0.008371599048441158</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4223840726503253</v>
+        <v>0.4223841133727762</v>
       </c>
       <c r="D68" t="n">
-        <v>0.9506178634729482</v>
+        <v>1.185370948690685</v>
       </c>
     </row>
     <row r="69">
@@ -1385,13 +1385,13 @@
         <v>41547</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>0.01015403751646389</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4235008845883866</v>
+        <v>0.4235008883743693</v>
       </c>
       <c r="D69" t="n">
-        <v>0.9506178634729482</v>
+        <v>1.197407249774617</v>
       </c>
     </row>
     <row r="70">
@@ -1399,13 +1399,13 @@
         <v>41578</v>
       </c>
       <c r="B70" t="n">
-        <v>0.003283458915271546</v>
+        <v>0.003283417642328118</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4379220036019602</v>
+        <v>0.4379221078215383</v>
       </c>
       <c r="D70" t="n">
-        <v>0.9537391781717848</v>
+        <v>1.201338837863579</v>
       </c>
     </row>
     <row r="71">
@@ -1413,13 +1413,13 @@
         <v>41608</v>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>-0.00552407040807395</v>
       </c>
       <c r="C71" t="n">
-        <v>0.4242946840697068</v>
+        <v>0.4242947199647702</v>
       </c>
       <c r="D71" t="n">
-        <v>0.9537391781717848</v>
+        <v>1.194702557539266</v>
       </c>
     </row>
     <row r="72">
@@ -1427,13 +1427,13 @@
         <v>41639</v>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>-0.007382348407860407</v>
       </c>
       <c r="C72" t="n">
-        <v>0.4350962956665848</v>
+        <v>0.4350962588128445</v>
       </c>
       <c r="D72" t="n">
-        <v>0.9537391781717848</v>
+        <v>1.18588284701575</v>
       </c>
     </row>
     <row r="73">
@@ -1441,13 +1441,13 @@
         <v>41670</v>
       </c>
       <c r="B73" t="n">
-        <v>0.0131377597549581</v>
+        <v>0.0131377634619608</v>
       </c>
       <c r="C73" t="n">
-        <v>0.4288812383238805</v>
+        <v>0.4288812730519602</v>
       </c>
       <c r="D73" t="n">
-        <v>0.9662691743634968</v>
+        <v>1.201462695353439</v>
       </c>
     </row>
     <row r="74">
@@ -1455,13 +1455,13 @@
         <v>41698</v>
       </c>
       <c r="B74" t="n">
-        <v>0.001733212511516683</v>
+        <v>0.001732943023378729</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4512097574845144</v>
+        <v>0.4512097544031852</v>
       </c>
       <c r="D74" t="n">
-        <v>0.9679439241859964</v>
+        <v>1.203544761749202</v>
       </c>
     </row>
     <row r="75">
@@ -1469,13 +1469,13 @@
         <v>41729</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.00240198454768155</v>
+        <v>-0.002401740316266422</v>
       </c>
       <c r="C75" t="n">
-        <v>0.4048857826981662</v>
+        <v>0.4048857468941978</v>
       </c>
       <c r="D75" t="n">
-        <v>0.9656189378370793</v>
+        <v>1.200654159772477</v>
       </c>
     </row>
     <row r="76">
@@ -1483,13 +1483,13 @@
         <v>41759</v>
       </c>
       <c r="B76" t="n">
-        <v>0.00310014003409512</v>
+        <v>0.003100060714624549</v>
       </c>
       <c r="C76" t="n">
-        <v>0.4088001399228535</v>
+        <v>0.4088001052916884</v>
       </c>
       <c r="D76" t="n">
-        <v>0.9686124917639484</v>
+        <v>1.204376260565039</v>
       </c>
     </row>
     <row r="77">
@@ -1497,13 +1497,13 @@
         <v>41790</v>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>0.005022745071496353</v>
       </c>
       <c r="C77" t="n">
-        <v>0.3794424564646061</v>
+        <v>0.3794425065989402</v>
       </c>
       <c r="D77" t="n">
-        <v>0.9686124917639484</v>
+        <v>1.210425535492019</v>
       </c>
     </row>
     <row r="78">
@@ -1511,13 +1511,13 @@
         <v>41820</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>0.001542308841831349</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6374013952512927</v>
+        <v>0.6374012789800247</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9686124917639484</v>
+        <v>1.212292385497787</v>
       </c>
     </row>
     <row r="79">
@@ -1525,13 +1525,13 @@
         <v>41851</v>
       </c>
       <c r="B79" t="n">
-        <v>-0.001443532101157134</v>
+        <v>-0.001442903685817986</v>
       </c>
       <c r="C79" t="n">
-        <v>0.6163907467029692</v>
+        <v>0.6163907160689616</v>
       </c>
       <c r="D79" t="n">
-        <v>0.9672142685385053</v>
+        <v>1.210543164346463</v>
       </c>
     </row>
     <row r="80">
@@ -1539,13 +1539,13 @@
         <v>41882</v>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>0.008025952039108988</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6528510828644036</v>
+        <v>0.6528510893790488</v>
       </c>
       <c r="D80" t="n">
-        <v>0.9672142685385053</v>
+        <v>1.220258925724779</v>
       </c>
     </row>
     <row r="81">
@@ -1553,13 +1553,13 @@
         <v>41912</v>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>-0.002694602779167405</v>
       </c>
       <c r="C81" t="n">
-        <v>0.6695357704942346</v>
+        <v>0.6695357744840849</v>
       </c>
       <c r="D81" t="n">
-        <v>0.9672142685385053</v>
+        <v>1.216970812632217</v>
       </c>
     </row>
     <row r="82">
@@ -1567,13 +1567,13 @@
         <v>41943</v>
       </c>
       <c r="B82" t="n">
-        <v>0.01044396537287548</v>
+        <v>0.01044432485690055</v>
       </c>
       <c r="C82" t="n">
-        <v>0.6843222114082317</v>
+        <v>0.6843222131439477</v>
       </c>
       <c r="D82" t="n">
-        <v>0.9773158208672725</v>
+        <v>1.229681251140714</v>
       </c>
     </row>
     <row r="83">
@@ -1581,13 +1581,13 @@
         <v>41973</v>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>0.007196097931772712</v>
       </c>
       <c r="C83" t="n">
-        <v>0.6981844955700232</v>
+        <v>0.6981845754813304</v>
       </c>
       <c r="D83" t="n">
-        <v>0.9773158208672725</v>
+        <v>1.238530157848788</v>
       </c>
     </row>
     <row r="84">
@@ -1595,13 +1595,13 @@
         <v>42004</v>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>0.002760876173626082</v>
       </c>
       <c r="C84" t="n">
-        <v>0.734970874027373</v>
+        <v>0.7349709437239358</v>
       </c>
       <c r="D84" t="n">
-        <v>0.9773158208672725</v>
+        <v>1.24194958625191</v>
       </c>
     </row>
     <row r="85">
@@ -1609,13 +1609,13 @@
         <v>42035</v>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>0.03123457575424259</v>
       </c>
       <c r="C85" t="n">
         <v>0.75</v>
       </c>
       <c r="D85" t="n">
-        <v>0.9773158208672725</v>
+        <v>1.280741354686645</v>
       </c>
     </row>
     <row r="86">
@@ -1623,13 +1623,13 @@
         <v>42063</v>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>-0.02312862783377636</v>
       </c>
       <c r="C86" t="n">
         <v>0.75</v>
       </c>
       <c r="D86" t="n">
-        <v>0.9773158208672725</v>
+        <v>1.251119564542771</v>
       </c>
     </row>
     <row r="87">
@@ -1637,13 +1637,13 @@
         <v>42094</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>0.01214771910202248</v>
       </c>
       <c r="C87" t="n">
         <v>0.75</v>
       </c>
       <c r="D87" t="n">
-        <v>0.9773158208672725</v>
+        <v>1.266317813575881</v>
       </c>
     </row>
     <row r="88">
@@ -1651,13 +1651,13 @@
         <v>42124</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.004802601331703121</v>
+        <v>-0.004801924406742858</v>
       </c>
       <c r="C88" t="n">
         <v>0.75</v>
       </c>
       <c r="D88" t="n">
-        <v>0.9726221626044809</v>
+        <v>1.260237051160178</v>
       </c>
     </row>
     <row r="89">
@@ -1665,13 +1665,13 @@
         <v>42155</v>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>-0.006472453915122513</v>
       </c>
       <c r="C89" t="n">
         <v>0.75</v>
       </c>
       <c r="D89" t="n">
-        <v>0.9726221626044809</v>
+        <v>1.252080224924414</v>
       </c>
     </row>
     <row r="90">
@@ -1679,13 +1679,13 @@
         <v>42185</v>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>-0.008962302115260161</v>
       </c>
       <c r="C90" t="n">
         <v>0.75</v>
       </c>
       <c r="D90" t="n">
-        <v>0.9726221626044809</v>
+        <v>1.240858703676099</v>
       </c>
     </row>
     <row r="91">
@@ -1693,13 +1693,13 @@
         <v>42216</v>
       </c>
       <c r="B91" t="n">
-        <v>0.01138842967573908</v>
+        <v>0.01138843072752577</v>
       </c>
       <c r="C91" t="n">
         <v>0.75</v>
       </c>
       <c r="D91" t="n">
-        <v>0.9836988017043673</v>
+        <v>1.254990137065561</v>
       </c>
     </row>
     <row r="92">
@@ -1707,13 +1707,13 @@
         <v>42247</v>
       </c>
       <c r="B92" t="n">
-        <v>0.0005921063045743521</v>
+        <v>0.000592515742878553</v>
       </c>
       <c r="C92" t="n">
         <v>0.75</v>
       </c>
       <c r="D92" t="n">
-        <v>0.9842812559666587</v>
+        <v>1.25573373847893</v>
       </c>
     </row>
     <row r="93">
@@ -1721,13 +1721,13 @@
         <v>42277</v>
       </c>
       <c r="B93" t="n">
-        <v>0.01173469284960414</v>
+        <v>0.01173455112379592</v>
       </c>
       <c r="C93" t="n">
         <v>0.75</v>
       </c>
       <c r="D93" t="n">
-        <v>0.9958314941830499</v>
+        <v>1.270469210230986</v>
       </c>
     </row>
     <row r="94">
@@ -1735,13 +1735,13 @@
         <v>42308</v>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>-0.006972836268901322</v>
       </c>
       <c r="C94" t="n">
         <v>0.75</v>
       </c>
       <c r="D94" t="n">
-        <v>0.9958314941830499</v>
+        <v>1.261610436443365</v>
       </c>
     </row>
     <row r="95">
@@ -1749,13 +1749,13 @@
         <v>42338</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>-0.001000852708468545</v>
       </c>
       <c r="C95" t="n">
         <v>0.75</v>
       </c>
       <c r="D95" t="n">
-        <v>0.9958314941830499</v>
+        <v>1.260347750221019</v>
       </c>
     </row>
     <row r="96">
@@ -1763,13 +1763,13 @@
         <v>42369</v>
       </c>
       <c r="B96" t="n">
-        <v>-0.003452550868136706</v>
+        <v>-0.00345232006147841</v>
       </c>
       <c r="C96" t="n">
         <v>0.75</v>
       </c>
       <c r="D96" t="n">
-        <v>0.9923933352932904</v>
+        <v>1.255996626398491</v>
       </c>
     </row>
     <row r="97">
@@ -1777,13 +1777,13 @@
         <v>42400</v>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>0.02287738316064055</v>
       </c>
       <c r="C97" t="n">
-        <v>0.7408831202765281</v>
+        <v>0.7408831228989434</v>
       </c>
       <c r="D97" t="n">
-        <v>0.9923933352932904</v>
+        <v>1.284730542469081</v>
       </c>
     </row>
     <row r="98">
@@ -1791,13 +1791,13 @@
         <v>42429</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>0.01282758701604916</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7390068787452939</v>
+        <v>0.7390068457027427</v>
       </c>
       <c r="D98" t="n">
-        <v>0.9923933352932904</v>
+        <v>1.30121053529478</v>
       </c>
     </row>
     <row r="99">
@@ -1805,13 +1805,13 @@
         <v>42460</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.000494759039296245</v>
+        <v>-0.0004946293418836424</v>
       </c>
       <c r="C99" t="n">
-        <v>0.748504536406205</v>
+        <v>0.7485044827644894</v>
       </c>
       <c r="D99" t="n">
-        <v>0.9919023397201167</v>
+        <v>1.300566918384055</v>
       </c>
     </row>
     <row r="100">
@@ -1819,13 +1819,13 @@
         <v>42490</v>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>-0.003162483494865478</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7225678879278936</v>
+        <v>0.7225678503743639</v>
       </c>
       <c r="D100" t="n">
-        <v>0.9919023397201167</v>
+        <v>1.296453896970697</v>
       </c>
     </row>
     <row r="101">
@@ -1833,13 +1833,13 @@
         <v>42521</v>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>0.001418094008757044</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7061375018104719</v>
+        <v>0.7061374280489946</v>
       </c>
       <c r="D101" t="n">
-        <v>0.9919023397201167</v>
+        <v>1.298292390474621</v>
       </c>
     </row>
     <row r="102">
@@ -1847,13 +1847,13 @@
         <v>42551</v>
       </c>
       <c r="B102" t="n">
-        <v>0.02135952928593573</v>
+        <v>0.02135976781213415</v>
       </c>
       <c r="C102" t="n">
-        <v>0.6939583865083663</v>
+        <v>0.6939583846327525</v>
       </c>
       <c r="D102" t="n">
-        <v>1.013088906794157</v>
+        <v>1.32602361448742</v>
       </c>
     </row>
     <row r="103">
@@ -1861,13 +1861,13 @@
         <v>42582</v>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>-0.0006128222665658721</v>
       </c>
       <c r="C103" t="n">
-        <v>0.6736557390639467</v>
+        <v>0.6736556839107454</v>
       </c>
       <c r="D103" t="n">
-        <v>1.013088906794157</v>
+        <v>1.32521099769047</v>
       </c>
     </row>
     <row r="104">
@@ -1875,13 +1875,13 @@
         <v>42613</v>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>-0.004276431420889803</v>
       </c>
       <c r="C104" t="n">
-        <v>0.6529891677420345</v>
+        <v>0.652989202666987</v>
       </c>
       <c r="D104" t="n">
-        <v>1.013088906794157</v>
+        <v>1.319543823740637</v>
       </c>
     </row>
     <row r="105">
@@ -1889,13 +1889,13 @@
         <v>42643</v>
       </c>
       <c r="B105" t="n">
-        <v>0.001592449331722631</v>
+        <v>0.001591825576854783</v>
       </c>
       <c r="C105" t="n">
-        <v>0.637275727248381</v>
+        <v>0.6372757330285517</v>
       </c>
       <c r="D105" t="n">
-        <v>1.014702199546756</v>
+        <v>1.321644307349048</v>
       </c>
     </row>
     <row r="106">
@@ -1903,13 +1903,13 @@
         <v>42674</v>
       </c>
       <c r="B106" t="n">
-        <v>-0.009080528480864585</v>
+        <v>-0.00907990540224758</v>
       </c>
       <c r="C106" t="n">
-        <v>0.6131806423941479</v>
+        <v>0.6131806513069561</v>
       </c>
       <c r="D106" t="n">
-        <v>1.005488167324176</v>
+        <v>1.3096439020629</v>
       </c>
     </row>
     <row r="107">
@@ -1917,13 +1917,13 @@
         <v>42704</v>
       </c>
       <c r="B107" t="n">
-        <v>-0.02611932080934504</v>
+        <v>-0.02611915484033288</v>
       </c>
       <c r="C107" t="n">
-        <v>0.6138817503925622</v>
+        <v>0.6138817950439084</v>
       </c>
       <c r="D107" t="n">
-        <v>0.9792254993118357</v>
+        <v>1.275437110199221</v>
       </c>
     </row>
     <row r="108">
@@ -1931,13 +1931,13 @@
         <v>42735</v>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>-0.0006622956144219101</v>
       </c>
       <c r="C108" t="n">
-        <v>0.5689416649904263</v>
+        <v>0.5689417180726805</v>
       </c>
       <c r="D108" t="n">
-        <v>0.9792254993118357</v>
+        <v>1.274592393794665</v>
       </c>
     </row>
     <row r="109">
@@ -1945,13 +1945,13 @@
         <v>42766</v>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>0.00137635875506569</v>
       </c>
       <c r="C109" t="n">
-        <v>0.5149446991891804</v>
+        <v>0.5149447199711967</v>
       </c>
       <c r="D109" t="n">
-        <v>0.9792254993118357</v>
+        <v>1.276346690195005</v>
       </c>
     </row>
     <row r="110">
@@ -1959,13 +1959,13 @@
         <v>42794</v>
       </c>
       <c r="B110" t="n">
-        <v>0.002186293734793916</v>
+        <v>0.002186380801679278</v>
       </c>
       <c r="C110" t="n">
         <v>0.25</v>
       </c>
       <c r="D110" t="n">
-        <v>0.9813663738859315</v>
+        <v>1.279137270094734</v>
       </c>
     </row>
     <row r="111">
@@ -1973,13 +1973,13 @@
         <v>42825</v>
       </c>
       <c r="B111" t="n">
-        <v>7.019741151982956e-05</v>
+        <v>7.038598060701964e-05</v>
       </c>
       <c r="C111" t="n">
         <v>0.25</v>
       </c>
       <c r="D111" t="n">
-        <v>0.9814352632651309</v>
+        <v>1.279227303425821</v>
       </c>
     </row>
     <row r="112">
@@ -1987,13 +1987,13 @@
         <v>42855</v>
       </c>
       <c r="B112" t="n">
-        <v>0</v>
+        <v>0.002941708635420358</v>
       </c>
       <c r="C112" t="n">
-        <v>0.2751967050658766</v>
+        <v>0.2751966657906701</v>
       </c>
       <c r="D112" t="n">
-        <v>0.9814352632651309</v>
+        <v>1.282990417430974</v>
       </c>
     </row>
     <row r="113">
@@ -2001,13 +2001,13 @@
         <v>42886</v>
       </c>
       <c r="B113" t="n">
-        <v>0</v>
+        <v>0.003865464374268323</v>
       </c>
       <c r="C113" t="n">
-        <v>0.3563918777519264</v>
+        <v>0.3563918868104455</v>
       </c>
       <c r="D113" t="n">
-        <v>0.9814352632651309</v>
+        <v>1.287949771182081</v>
       </c>
     </row>
     <row r="114">
@@ -2015,13 +2015,13 @@
         <v>42916</v>
       </c>
       <c r="B114" t="n">
-        <v>-0.001253776971611931</v>
+        <v>-0.001253551906157029</v>
       </c>
       <c r="C114" t="n">
-        <v>0.3726869533742163</v>
+        <v>0.3726869973653935</v>
       </c>
       <c r="D114" t="n">
-        <v>0.9802047623329212</v>
+        <v>1.286335259291381</v>
       </c>
     </row>
     <row r="115">
@@ -2029,13 +2029,13 @@
         <v>42947</v>
       </c>
       <c r="B115" t="n">
-        <v>0.001689417296148682</v>
+        <v>0.001689476743619224</v>
       </c>
       <c r="C115" t="n">
-        <v>0.3981428719901088</v>
+        <v>0.3981428779388534</v>
       </c>
       <c r="D115" t="n">
-        <v>0.9818607372121736</v>
+        <v>1.288508492796452</v>
       </c>
     </row>
     <row r="116">
@@ -2043,13 +2043,13 @@
         <v>42978</v>
       </c>
       <c r="B116" t="n">
-        <v>0.005547705173328987</v>
+        <v>0.005547542143036211</v>
       </c>
       <c r="C116" t="n">
-        <v>0.328151663710693</v>
+        <v>0.3281516758550832</v>
       </c>
       <c r="D116" t="n">
-        <v>0.9873078111034942</v>
+        <v>1.2956565479619</v>
       </c>
     </row>
     <row r="117">
@@ -2057,13 +2057,13 @@
         <v>43008</v>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>-0.004674965593101907</v>
       </c>
       <c r="C117" t="n">
-        <v>0.333738075286623</v>
+        <v>0.333738086689153</v>
       </c>
       <c r="D117" t="n">
-        <v>0.9873078111034942</v>
+        <v>1.289599398179701</v>
       </c>
     </row>
     <row r="118">
@@ -2071,13 +2071,13 @@
         <v>43039</v>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>0.000160929224796249</v>
       </c>
       <c r="C118" t="n">
-        <v>0.351354038113854</v>
+        <v>0.3513541217616462</v>
       </c>
       <c r="D118" t="n">
-        <v>0.9873078111034942</v>
+        <v>1.289806932411148</v>
       </c>
     </row>
     <row r="119">
@@ -2085,13 +2085,13 @@
         <v>43069</v>
       </c>
       <c r="B119" t="n">
-        <v>-0.0005617104852906587</v>
+        <v>-0.0005614592348840673</v>
       </c>
       <c r="C119" t="n">
-        <v>0.3319429591957537</v>
+        <v>0.3319430447548679</v>
       </c>
       <c r="D119" t="n">
-        <v>0.986753229953788</v>
+        <v>1.289082758397728</v>
       </c>
     </row>
     <row r="120">
@@ -2099,13 +2099,13 @@
         <v>43100</v>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>-0.0005270528293642106</v>
       </c>
       <c r="C120" t="n">
-        <v>0.5931088090577288</v>
+        <v>0.5931088178276638</v>
       </c>
       <c r="D120" t="n">
-        <v>0.986753229953788</v>
+        <v>1.28840334368263</v>
       </c>
     </row>
     <row r="121">
@@ -2113,13 +2113,13 @@
         <v>43131</v>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>-0.01028375666215707</v>
       </c>
       <c r="C121" t="n">
-        <v>0.5905642343383459</v>
+        <v>0.590564136258484</v>
       </c>
       <c r="D121" t="n">
-        <v>0.986753229953788</v>
+        <v>1.275153717213488</v>
       </c>
     </row>
     <row r="122">
@@ -2127,13 +2127,13 @@
         <v>43159</v>
       </c>
       <c r="B122" t="n">
-        <v>-0.002499461098858688</v>
+        <v>-0.002499489983225625</v>
       </c>
       <c r="C122" t="n">
-        <v>0.3278758784485775</v>
+        <v>0.327875889995801</v>
       </c>
       <c r="D122" t="n">
-        <v>0.9842868786413453</v>
+        <v>1.27196648327024</v>
       </c>
     </row>
     <row r="123">
@@ -2141,13 +2141,13 @@
         <v>43190</v>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>0.005098591374470805</v>
       </c>
       <c r="C123" t="n">
-        <v>0.3396275610021233</v>
+        <v>0.3396275368268207</v>
       </c>
       <c r="D123" t="n">
-        <v>0.9842868786413453</v>
+        <v>1.278451720610458</v>
       </c>
     </row>
     <row r="124">
@@ -2155,13 +2155,13 @@
         <v>43220</v>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>-0.00344955490295376</v>
       </c>
       <c r="C124" t="n">
-        <v>0.3056623277389066</v>
+        <v>0.3056623754741881</v>
       </c>
       <c r="D124" t="n">
-        <v>0.9842868786413453</v>
+        <v>1.274041631209436</v>
       </c>
     </row>
     <row r="125">
@@ -2169,13 +2169,13 @@
         <v>43251</v>
       </c>
       <c r="B125" t="n">
-        <v>0.003779222963620791</v>
+        <v>0.003778975618314315</v>
       </c>
       <c r="C125" t="n">
-        <v>0.2727107200733095</v>
+        <v>0.2727107768513349</v>
       </c>
       <c r="D125" t="n">
-        <v>0.9880067182158975</v>
+        <v>1.278856203470494</v>
       </c>
     </row>
     <row r="126">
@@ -2183,13 +2183,13 @@
         <v>43281</v>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>0.001330576740926792</v>
       </c>
       <c r="C126" t="n">
         <v>0.25</v>
       </c>
       <c r="D126" t="n">
-        <v>0.9880067182158975</v>
+        <v>1.280557819789822</v>
       </c>
     </row>
     <row r="127">
@@ -2197,13 +2197,13 @@
         <v>43312</v>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>-2.75398929634582e-05</v>
       </c>
       <c r="C127" t="n">
-        <v>0.2544203946561677</v>
+        <v>0.2544204057941843</v>
       </c>
       <c r="D127" t="n">
-        <v>0.9880067182158975</v>
+        <v>1.280522553364532</v>
       </c>
     </row>
     <row r="128">
@@ -2211,13 +2211,13 @@
         <v>43343</v>
       </c>
       <c r="B128" t="n">
-        <v>0.004046626734571212</v>
+        <v>0.00404622035077525</v>
       </c>
       <c r="C128" t="n">
-        <v>0.2876644705588225</v>
+        <v>0.2876645700166626</v>
       </c>
       <c r="D128" t="n">
-        <v>0.9920048126157658</v>
+        <v>1.285703829779582</v>
       </c>
     </row>
     <row r="129">
@@ -2225,13 +2225,13 @@
         <v>43373</v>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>-0.003237727539148214</v>
       </c>
       <c r="C129" t="n">
-        <v>0.2935745730149633</v>
+        <v>0.2935745872782655</v>
       </c>
       <c r="D129" t="n">
-        <v>0.9920048126157658</v>
+        <v>1.281541071082716</v>
       </c>
     </row>
     <row r="130">
@@ -2239,13 +2239,13 @@
         <v>43404</v>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>0.001030984469880583</v>
       </c>
       <c r="C130" t="n">
-        <v>0.2851205371088266</v>
+        <v>0.2851203899059838</v>
       </c>
       <c r="D130" t="n">
-        <v>0.9920048126157658</v>
+        <v>1.282862320024517</v>
       </c>
     </row>
     <row r="131">
@@ -2253,13 +2253,13 @@
         <v>43434</v>
       </c>
       <c r="B131" t="n">
-        <v>0.005762325788958567</v>
+        <v>0.005761971156007004</v>
       </c>
       <c r="C131" t="n">
-        <v>0.3410944909670695</v>
+        <v>0.3410944630004666</v>
       </c>
       <c r="D131" t="n">
-        <v>0.9977210675302726</v>
+        <v>1.290254135709626</v>
       </c>
     </row>
     <row r="132">
@@ -2267,13 +2267,13 @@
         <v>43465</v>
       </c>
       <c r="B132" t="n">
-        <v>0.01239928936753396</v>
+        <v>0.01239947191614936</v>
       </c>
       <c r="C132" t="n">
-        <v>0.4032755438191494</v>
+        <v>0.4032754756365195</v>
       </c>
       <c r="D132" t="n">
-        <v>1.010092099754665</v>
+        <v>1.306252605630053</v>
       </c>
     </row>
     <row r="133">
@@ -2281,13 +2281,13 @@
         <v>43496</v>
       </c>
       <c r="B133" t="n">
-        <v>0.003808907928235797</v>
+        <v>0.003809132132565569</v>
       </c>
       <c r="C133" t="n">
-        <v>0.4312107029686896</v>
+        <v>0.4312108311441157</v>
       </c>
       <c r="D133" t="n">
-        <v>1.013939447561669</v>
+        <v>1.311228294403406</v>
       </c>
     </row>
     <row r="134">
@@ -2295,13 +2295,13 @@
         <v>43524</v>
       </c>
       <c r="B134" t="n">
-        <v>-0.002857504086753399</v>
+        <v>-0.002857661320500182</v>
       </c>
       <c r="C134" t="n">
-        <v>0.66247557356189</v>
+        <v>0.6624755748655577</v>
       </c>
       <c r="D134" t="n">
-        <v>1.011042111446541</v>
+        <v>1.307481248024144</v>
       </c>
     </row>
     <row r="135">
@@ -2309,13 +2309,13 @@
         <v>43555</v>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>0.0130626556768637</v>
       </c>
       <c r="C135" t="n">
-        <v>0.6339857007555003</v>
+        <v>0.6339857390175194</v>
       </c>
       <c r="D135" t="n">
-        <v>1.011042111446541</v>
+        <v>1.324560425371039</v>
       </c>
     </row>
     <row r="136">
@@ -2323,13 +2323,13 @@
         <v>43585</v>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>0.001719155258890379</v>
       </c>
       <c r="C136" t="n">
-        <v>0.6471852535523843</v>
+        <v>0.647185225363764</v>
       </c>
       <c r="D136" t="n">
-        <v>1.011042111446541</v>
+        <v>1.326837550392034</v>
       </c>
     </row>
     <row r="137">
@@ -2337,13 +2337,13 @@
         <v>43616</v>
       </c>
       <c r="B137" t="n">
-        <v>0.0207788993601413</v>
+        <v>0.02077897256941648</v>
       </c>
       <c r="C137" t="n">
-        <v>0.6577623753079959</v>
+        <v>0.6577623795245667</v>
       </c>
       <c r="D137" t="n">
-        <v>1.032050453729153</v>
+        <v>1.354407871455702</v>
       </c>
     </row>
     <row r="138">
@@ -2351,13 +2351,13 @@
         <v>43646</v>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>0.008145563002246703</v>
       </c>
       <c r="C138" t="n">
-        <v>0.6986694273727787</v>
+        <v>0.6986694191543602</v>
       </c>
       <c r="D138" t="n">
-        <v>1.032050453729153</v>
+        <v>1.365440286103383</v>
       </c>
     </row>
     <row r="139">
@@ -2365,13 +2365,13 @@
         <v>43677</v>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>0.001713903354620524</v>
       </c>
       <c r="C139" t="n">
-        <v>0.6659212044949752</v>
+        <v>0.6659212362364716</v>
       </c>
       <c r="D139" t="n">
-        <v>1.032050453729153</v>
+        <v>1.36778051879027</v>
       </c>
     </row>
     <row r="140">
@@ -2379,13 +2379,13 @@
         <v>43708</v>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>0.02842716808214055</v>
       </c>
       <c r="C140" t="n">
-        <v>0.6649211322262742</v>
+        <v>0.664921135847661</v>
       </c>
       <c r="D140" t="n">
-        <v>1.032050453729153</v>
+        <v>1.406662645497398</v>
       </c>
     </row>
     <row r="141">
@@ -2393,13 +2393,13 @@
         <v>43738</v>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>-0.009238788533719205</v>
       </c>
       <c r="C141" t="n">
-        <v>0.6900938646258732</v>
+        <v>0.6900939263149007</v>
       </c>
       <c r="D141" t="n">
-        <v>1.032050453729153</v>
+        <v>1.393666786777366</v>
       </c>
     </row>
     <row r="142">
@@ -2407,13 +2407,13 @@
         <v>43769</v>
       </c>
       <c r="B142" t="n">
-        <v>0.001797372283239479</v>
+        <v>0.001797210069076436</v>
       </c>
       <c r="C142" t="n">
-        <v>0.6991173582023383</v>
+        <v>0.6991174104748898</v>
       </c>
       <c r="D142" t="n">
-        <v>1.033905432609591</v>
+        <v>1.396171498759499</v>
       </c>
     </row>
     <row r="143">
@@ -2421,13 +2421,13 @@
         <v>43799</v>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>-0.006525323523424072</v>
       </c>
       <c r="C143" t="n">
-        <v>0.6626498831253183</v>
+        <v>0.662649882935148</v>
       </c>
       <c r="D143" t="n">
-        <v>1.033905432609591</v>
+        <v>1.38706102803591</v>
       </c>
     </row>
     <row r="144">
@@ -2435,13 +2435,13 @@
         <v>43830</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>-0.003093758277560257</v>
       </c>
       <c r="C144" t="n">
-        <v>0.6122508473075328</v>
+        <v>0.6122509323802198</v>
       </c>
       <c r="D144" t="n">
-        <v>1.033905432609591</v>
+        <v>1.382769796498942</v>
       </c>
     </row>
     <row r="145">
@@ -2449,13 +2449,13 @@
         <v>43861</v>
       </c>
       <c r="B145" t="n">
-        <v>0.01979272997693522</v>
+        <v>0.01979291498201509</v>
       </c>
       <c r="C145" t="n">
-        <v>0.5556648370960907</v>
+        <v>0.555664936842355</v>
       </c>
       <c r="D145" t="n">
-        <v>1.054369243658919</v>
+        <v>1.410138841520744</v>
       </c>
     </row>
     <row r="146">
@@ -2463,13 +2463,13 @@
         <v>43890</v>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>0.01922890319833979</v>
       </c>
       <c r="C146" t="n">
-        <v>0.6470069482253763</v>
+        <v>0.647006985050615</v>
       </c>
       <c r="D146" t="n">
-        <v>1.054369243658919</v>
+        <v>1.437254264800565</v>
       </c>
     </row>
     <row r="147">
@@ -2477,13 +2477,13 @@
         <v>43921</v>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>0.0265181802703828</v>
       </c>
       <c r="C147" t="n">
-        <v>0.6844897865523523</v>
+        <v>0.6844897061844131</v>
       </c>
       <c r="D147" t="n">
-        <v>1.054369243658919</v>
+        <v>1.475367632488923</v>
       </c>
     </row>
     <row r="148">
@@ -2491,13 +2491,13 @@
         <v>43951</v>
       </c>
       <c r="B148" t="n">
-        <v>0.002015431617686713</v>
+        <v>0.002015546800772923</v>
       </c>
       <c r="C148" t="n">
         <v>0.75</v>
       </c>
       <c r="D148" t="n">
-        <v>1.056494252769306</v>
+        <v>1.47834130500055</v>
       </c>
     </row>
     <row r="149">
@@ -2505,13 +2505,13 @@
         <v>43982</v>
       </c>
       <c r="B149" t="n">
-        <v>0</v>
+        <v>0.002142824215411981</v>
       </c>
       <c r="C149" t="n">
         <v>0.75</v>
       </c>
       <c r="D149" t="n">
-        <v>1.056494252769306</v>
+        <v>1.481509130547549</v>
       </c>
     </row>
     <row r="150">
@@ -2519,13 +2519,13 @@
         <v>44012</v>
       </c>
       <c r="B150" t="n">
-        <v>0</v>
+        <v>0.0005683567800850803</v>
       </c>
       <c r="C150" t="n">
-        <v>0.7279529523593287</v>
+        <v>0.7279530149792915</v>
       </c>
       <c r="D150" t="n">
-        <v>1.056494252769306</v>
+        <v>1.482351156306654</v>
       </c>
     </row>
     <row r="151">
@@ -2533,13 +2533,13 @@
         <v>44043</v>
       </c>
       <c r="B151" t="n">
-        <v>0.006160745483707937</v>
+        <v>0.006160985328202764</v>
       </c>
       <c r="C151" t="n">
-        <v>0.7176908611847685</v>
+        <v>0.7176907828947323</v>
       </c>
       <c r="D151" t="n">
-        <v>1.063003044965618</v>
+        <v>1.491483900031904</v>
       </c>
     </row>
     <row r="152">
@@ -2547,13 +2547,13 @@
         <v>44074</v>
       </c>
       <c r="B152" t="n">
-        <v>-0.006644783999891854</v>
+        <v>-0.006644833173714911</v>
       </c>
       <c r="C152" t="n">
-        <v>0.6851226232498039</v>
+        <v>0.6851225801121853</v>
       </c>
       <c r="D152" t="n">
-        <v>1.055939619340594</v>
+        <v>1.48157323833491</v>
       </c>
     </row>
     <row r="153">
@@ -2561,13 +2561,13 @@
         <v>44104</v>
       </c>
       <c r="B153" t="n">
-        <v>0.002054420722007326</v>
+        <v>0.002054468096928867</v>
       </c>
       <c r="C153" t="n">
-        <v>0.6500427723137689</v>
+        <v>0.6500427705951801</v>
       </c>
       <c r="D153" t="n">
-        <v>1.058108963575755</v>
+        <v>1.484617083286333</v>
       </c>
     </row>
     <row r="154">
@@ -2575,13 +2575,13 @@
         <v>44135</v>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>-0.008115863124562686</v>
       </c>
       <c r="C154" t="n">
-        <v>0.6728531011285326</v>
+        <v>0.6728530633207561</v>
       </c>
       <c r="D154" t="n">
-        <v>1.058108963575755</v>
+        <v>1.472568134245994</v>
       </c>
     </row>
     <row r="155">
@@ -2589,13 +2589,13 @@
         <v>44165</v>
       </c>
       <c r="B155" t="n">
-        <v>0</v>
+        <v>0.001148406368791494</v>
       </c>
       <c r="C155" t="n">
-        <v>0.709301542916468</v>
+        <v>0.709301569324536</v>
       </c>
       <c r="D155" t="n">
-        <v>1.058108963575755</v>
+        <v>1.474259240869841</v>
       </c>
     </row>
     <row r="156">
@@ -2603,13 +2603,13 @@
         <v>44196</v>
       </c>
       <c r="B156" t="n">
-        <v>-0.001545053446064514</v>
+        <v>-0.001545026388414036</v>
       </c>
       <c r="C156" t="n">
-        <v>0.6526830972900506</v>
+        <v>0.6526830950806883</v>
       </c>
       <c r="D156" t="n">
-        <v>1.056474128675271</v>
+        <v>1.471981471439334</v>
       </c>
     </row>
     <row r="157">
@@ -2617,13 +2617,13 @@
         <v>44227</v>
       </c>
       <c r="B157" t="n">
-        <v>0</v>
+        <v>-0.006409665382025401</v>
       </c>
       <c r="C157" t="n">
-        <v>0.6617150404618696</v>
+        <v>0.6617151110784857</v>
       </c>
       <c r="D157" t="n">
-        <v>1.056474128675271</v>
+        <v>1.462546562758866</v>
       </c>
     </row>
     <row r="158">
@@ -2631,13 +2631,13 @@
         <v>44255</v>
       </c>
       <c r="B158" t="n">
-        <v>0</v>
+        <v>-0.0153712039748622</v>
       </c>
       <c r="C158" t="n">
-        <v>0.5889642298494011</v>
+        <v>0.5889641963134167</v>
       </c>
       <c r="D158" t="n">
-        <v>1.056474128675271</v>
+        <v>1.440065461219966</v>
       </c>
     </row>
     <row r="159">
@@ -2645,13 +2645,13 @@
         <v>44286</v>
       </c>
       <c r="B159" t="n">
-        <v>0</v>
+        <v>-0.005689680974598827</v>
       </c>
       <c r="C159" t="n">
         <v>0.25</v>
       </c>
       <c r="D159" t="n">
-        <v>1.056474128675271</v>
+        <v>1.431871948163086</v>
       </c>
     </row>
     <row r="160">
@@ -2659,13 +2659,13 @@
         <v>44316</v>
       </c>
       <c r="B160" t="n">
-        <v>0.002503088152636117</v>
+        <v>0.002503048607208895</v>
       </c>
       <c r="C160" t="n">
         <v>0.25</v>
       </c>
       <c r="D160" t="n">
-        <v>1.059118576550325</v>
+        <v>1.435455993248637</v>
       </c>
     </row>
     <row r="161">
@@ -2673,13 +2673,13 @@
         <v>44347</v>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>0.0008522136570479713</v>
       </c>
       <c r="C161" t="n">
         <v>0.25</v>
       </c>
       <c r="D161" t="n">
-        <v>1.059118576550325</v>
+        <v>1.436679308450175</v>
       </c>
     </row>
     <row r="162">
@@ -2687,13 +2687,13 @@
         <v>44377</v>
       </c>
       <c r="B162" t="n">
-        <v>0</v>
+        <v>0.002520830398929315</v>
       </c>
       <c r="C162" t="n">
         <v>0.25</v>
       </c>
       <c r="D162" t="n">
-        <v>1.059118576550325</v>
+        <v>1.440300933324429</v>
       </c>
     </row>
     <row r="163">
@@ -2701,13 +2701,13 @@
         <v>44408</v>
       </c>
       <c r="B163" t="n">
-        <v>0</v>
+        <v>0.006011838134151587</v>
       </c>
       <c r="C163" t="n">
         <v>0.25</v>
       </c>
       <c r="D163" t="n">
-        <v>1.059118576550325</v>
+        <v>1.448959789400043</v>
       </c>
     </row>
     <row r="164">
@@ -2715,13 +2715,13 @@
         <v>44439</v>
       </c>
       <c r="B164" t="n">
-        <v>0</v>
+        <v>-0.002155279698597597</v>
       </c>
       <c r="C164" t="n">
         <v>0.25</v>
       </c>
       <c r="D164" t="n">
-        <v>1.059118576550325</v>
+        <v>1.445836875781864</v>
       </c>
     </row>
     <row r="165">
@@ -2729,13 +2729,13 @@
         <v>44469</v>
       </c>
       <c r="B165" t="n">
-        <v>-0.003910300542024788</v>
+        <v>-0.003911000061547897</v>
       </c>
       <c r="C165" t="n">
         <v>0.25</v>
       </c>
       <c r="D165" t="n">
-        <v>1.054977104606372</v>
+        <v>1.440182207671693</v>
       </c>
     </row>
     <row r="166">
@@ -2743,13 +2743,13 @@
         <v>44500</v>
       </c>
       <c r="B166" t="n">
-        <v>0</v>
+        <v>-0.001208532028499651</v>
       </c>
       <c r="C166" t="n">
         <v>0.25</v>
       </c>
       <c r="D166" t="n">
-        <v>1.054977104606372</v>
+        <v>1.438441701346847</v>
       </c>
     </row>
     <row r="167">
@@ -2757,13 +2757,13 @@
         <v>44530</v>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>0.002586099631073012</v>
       </c>
       <c r="C167" t="n">
         <v>0.25</v>
       </c>
       <c r="D167" t="n">
-        <v>1.054977104606372</v>
+        <v>1.44216165490002</v>
       </c>
     </row>
     <row r="168">
@@ -2771,13 +2771,13 @@
         <v>44561</v>
       </c>
       <c r="B168" t="n">
-        <v>-0.00131010677760402</v>
+        <v>-0.001310069269914997</v>
       </c>
       <c r="C168" t="n">
         <v>0.25</v>
       </c>
       <c r="D168" t="n">
-        <v>1.05359497195141</v>
+        <v>1.440272323233685</v>
       </c>
     </row>
     <row r="169">
@@ -2785,13 +2785,13 @@
         <v>44592</v>
       </c>
       <c r="B169" t="n">
-        <v>-0.005282550721885088</v>
+        <v>-0.005282625931139563</v>
       </c>
       <c r="C169" t="n">
         <v>0.25</v>
       </c>
       <c r="D169" t="n">
-        <v>1.048029303071753</v>
+        <v>1.432663903311068</v>
       </c>
     </row>
     <row r="170">
@@ -2799,13 +2799,13 @@
         <v>44620</v>
       </c>
       <c r="B170" t="n">
-        <v>-0.0009240939217473971</v>
+        <v>-0.0009246408658898011</v>
       </c>
       <c r="C170" t="n">
         <v>0.25</v>
       </c>
       <c r="D170" t="n">
-        <v>1.047060825562972</v>
+        <v>1.431339203718982</v>
       </c>
     </row>
     <row r="171">
@@ -2813,13 +2813,13 @@
         <v>44651</v>
       </c>
       <c r="B171" t="n">
-        <v>-0.00980777203045274</v>
+        <v>-0.009807203490647671</v>
       </c>
       <c r="C171" t="n">
         <v>0.25</v>
       </c>
       <c r="D171" t="n">
-        <v>1.036791491683832</v>
+        <v>1.417301768883968</v>
       </c>
     </row>
     <row r="172">
@@ -2827,13 +2827,13 @@
         <v>44681</v>
       </c>
       <c r="B172" t="n">
-        <v>0</v>
+        <v>-0.01235443055148075</v>
       </c>
       <c r="C172" t="n">
         <v>0.25</v>
       </c>
       <c r="D172" t="n">
-        <v>1.036791491683832</v>
+        <v>1.3997918126098</v>
       </c>
     </row>
     <row r="173">
@@ -2841,13 +2841,13 @@
         <v>44712</v>
       </c>
       <c r="B173" t="n">
-        <v>0</v>
+        <v>0.003598171885980177</v>
       </c>
       <c r="C173" t="n">
         <v>0.25</v>
       </c>
       <c r="D173" t="n">
-        <v>1.036791491683832</v>
+        <v>1.404828504156158</v>
       </c>
     </row>
     <row r="174">
@@ -2855,13 +2855,13 @@
         <v>44742</v>
       </c>
       <c r="B174" t="n">
-        <v>-0.001575980491778945</v>
+        <v>-0.001576326673110224</v>
       </c>
       <c r="C174" t="n">
         <v>0.25</v>
       </c>
       <c r="D174" t="n">
-        <v>1.035157528518896</v>
+        <v>1.402614035513911</v>
       </c>
     </row>
     <row r="175">
@@ -2869,13 +2869,13 @@
         <v>44773</v>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>0.009237196717462591</v>
       </c>
       <c r="C175" t="n">
         <v>0.25</v>
       </c>
       <c r="D175" t="n">
-        <v>1.035157528518896</v>
+        <v>1.415570257278627</v>
       </c>
     </row>
     <row r="176">
@@ -2883,13 +2883,13 @@
         <v>44804</v>
       </c>
       <c r="B176" t="n">
-        <v>0</v>
+        <v>-0.009636859570758664</v>
       </c>
       <c r="C176" t="n">
         <v>0.25</v>
       </c>
       <c r="D176" t="n">
-        <v>1.035157528518896</v>
+        <v>1.40192860549669</v>
       </c>
     </row>
     <row r="177">
@@ -2897,13 +2897,13 @@
         <v>44834</v>
       </c>
       <c r="B177" t="n">
-        <v>-0.01028642585360674</v>
+        <v>-0.01028656219275409</v>
       </c>
       <c r="C177" t="n">
         <v>0.25</v>
       </c>
       <c r="D177" t="n">
-        <v>1.024509457354984</v>
+        <v>1.387507579706447</v>
       </c>
     </row>
     <row r="178">
@@ -2911,13 +2911,13 @@
         <v>44865</v>
       </c>
       <c r="B178" t="n">
-        <v>-0.003417467469062724</v>
+        <v>-0.003417736607656383</v>
       </c>
       <c r="C178" t="n">
-        <v>0.3102500001706751</v>
+        <v>0.3102500555825246</v>
       </c>
       <c r="D178" t="n">
-        <v>1.021008229612726</v>
+        <v>1.382765444257884</v>
       </c>
     </row>
     <row r="179">
@@ -2925,13 +2925,13 @@
         <v>44895</v>
       </c>
       <c r="B179" t="n">
-        <v>0.01340966879267804</v>
+        <v>0.01340954093857033</v>
       </c>
       <c r="C179" t="n">
-        <v>0.3111204895355094</v>
+        <v>0.3111204386594502</v>
       </c>
       <c r="D179" t="n">
-        <v>1.034699611806431</v>
+        <v>1.4013076940911</v>
       </c>
     </row>
     <row r="180">
@@ -2939,13 +2939,13 @@
         <v>44926</v>
       </c>
       <c r="B180" t="n">
-        <v>0</v>
+        <v>0.00101023377788751</v>
       </c>
       <c r="C180" t="n">
         <v>0.25</v>
       </c>
       <c r="D180" t="n">
-        <v>1.034699611806431</v>
+        <v>1.402723342456885</v>
       </c>
     </row>
     <row r="181">
@@ -2953,13 +2953,13 @@
         <v>44957</v>
       </c>
       <c r="B181" t="n">
-        <v>0</v>
+        <v>0.01024513865019463</v>
       </c>
       <c r="C181" t="n">
-        <v>0.3001305969526212</v>
+        <v>0.3001306618826927</v>
       </c>
       <c r="D181" t="n">
-        <v>1.034699611806431</v>
+        <v>1.41709443758822</v>
       </c>
     </row>
     <row r="182">
@@ -2967,13 +2967,13 @@
         <v>44985</v>
       </c>
       <c r="B182" t="n">
-        <v>-0.008723426129002331</v>
+        <v>-0.008722939830905239</v>
       </c>
       <c r="C182" t="n">
-        <v>0.3368091565432284</v>
+        <v>0.3368091085932775</v>
       </c>
       <c r="D182" t="n">
-        <v>1.025673486177131</v>
+        <v>1.404733208074428</v>
       </c>
     </row>
     <row r="183">
@@ -2981,13 +2981,13 @@
         <v>45016</v>
       </c>
       <c r="B183" t="n">
-        <v>0.01697728530554002</v>
+        <v>0.01697690621460872</v>
       </c>
       <c r="C183" t="n">
-        <v>0.3909209124506307</v>
+        <v>0.3909209130974324</v>
       </c>
       <c r="D183" t="n">
-        <v>1.043086637582288</v>
+        <v>1.428581232004454</v>
       </c>
     </row>
     <row r="184">
@@ -2995,13 +2995,13 @@
         <v>45046</v>
       </c>
       <c r="B184" t="n">
-        <v>0</v>
+        <v>0.0004819315672383116</v>
       </c>
       <c r="C184" t="n">
-        <v>0.431010561502662</v>
+        <v>0.4310105598163054</v>
       </c>
       <c r="D184" t="n">
-        <v>1.043086637582288</v>
+        <v>1.429269710396521</v>
       </c>
     </row>
     <row r="185">
@@ -3009,13 +3009,13 @@
         <v>45077</v>
       </c>
       <c r="B185" t="n">
-        <v>0</v>
+        <v>0.0007903687862298669</v>
       </c>
       <c r="C185" t="n">
-        <v>0.4602065609884485</v>
+        <v>0.4602065950732496</v>
       </c>
       <c r="D185" t="n">
-        <v>1.043086637582288</v>
+        <v>1.430399360562722</v>
       </c>
     </row>
     <row r="186">
@@ -3023,13 +3023,13 @@
         <v>45107</v>
       </c>
       <c r="B186" t="n">
-        <v>-0.003969709809855467</v>
+        <v>-0.003969818567975328</v>
       </c>
       <c r="C186" t="n">
-        <v>0.4998032086429878</v>
+        <v>0.4998031666276369</v>
       </c>
       <c r="D186" t="n">
-        <v>1.038945886324548</v>
+        <v>1.42472093462154</v>
       </c>
     </row>
     <row r="187">
@@ -3037,13 +3037,13 @@
         <v>45138</v>
       </c>
       <c r="B187" t="n">
-        <v>-0.0008911023993022241</v>
+        <v>-0.0008909873273591391</v>
       </c>
       <c r="C187" t="n">
-        <v>0.4578656922294118</v>
+        <v>0.4578656946382567</v>
       </c>
       <c r="D187" t="n">
-        <v>1.038020079152499</v>
+        <v>1.423451526323769</v>
       </c>
     </row>
     <row r="188">
@@ -3051,13 +3051,13 @@
         <v>45169</v>
       </c>
       <c r="B188" t="n">
-        <v>-0.0001034496172266546</v>
+        <v>-0.0001036495802426542</v>
       </c>
       <c r="C188" t="n">
-        <v>0.4130379587464973</v>
+        <v>0.4130379201194854</v>
       </c>
       <c r="D188" t="n">
-        <v>1.037912696372637</v>
+        <v>1.42330398617057</v>
       </c>
     </row>
     <row r="189">
@@ -3065,13 +3065,13 @@
         <v>45199</v>
       </c>
       <c r="B189" t="n">
-        <v>0</v>
+        <v>-0.01354675064408846</v>
       </c>
       <c r="C189" t="n">
-        <v>0.4077369679552783</v>
+        <v>0.407737006801138</v>
       </c>
       <c r="D189" t="n">
-        <v>1.037912696372637</v>
+        <v>1.40402284197918</v>
       </c>
     </row>
     <row r="190">
@@ -3079,13 +3079,13 @@
         <v>45230</v>
       </c>
       <c r="B190" t="n">
-        <v>0</v>
+        <v>-0.001572803175239554</v>
       </c>
       <c r="C190" t="n">
-        <v>0.3716645489708902</v>
+        <v>0.371664507339291</v>
       </c>
       <c r="D190" t="n">
-        <v>1.037912696372637</v>
+        <v>1.401814590395207</v>
       </c>
     </row>
     <row r="191">
@@ -3093,13 +3093,13 @@
         <v>45260</v>
       </c>
       <c r="B191" t="n">
-        <v>0.02095692533356018</v>
+        <v>0.02095706100454684</v>
       </c>
       <c r="C191" t="n">
-        <v>0.39828572864997</v>
+        <v>0.3982857289836013</v>
       </c>
       <c r="D191" t="n">
-        <v>1.059664155253273</v>
+        <v>1.431192504283183</v>
       </c>
     </row>
     <row r="192">
@@ -3107,13 +3107,13 @@
         <v>45291</v>
       </c>
       <c r="B192" t="n">
-        <v>0</v>
+        <v>0.01665388056523194</v>
       </c>
       <c r="C192" t="n">
-        <v>0.4164248757325223</v>
+        <v>0.416424875049738</v>
       </c>
       <c r="D192" t="n">
-        <v>1.059664155253273</v>
+        <v>1.45502741331537</v>
       </c>
     </row>
     <row r="193">
@@ -3121,13 +3121,13 @@
         <v>45322</v>
       </c>
       <c r="B193" t="n">
-        <v>0</v>
+        <v>0.004290347951095227</v>
       </c>
       <c r="C193" t="n">
-        <v>0.4149465510916716</v>
+        <v>0.4149465504870243</v>
       </c>
       <c r="D193" t="n">
-        <v>1.059664155253273</v>
+        <v>1.461269987196875</v>
       </c>
     </row>
     <row r="194">
@@ -3135,13 +3135,13 @@
         <v>45351</v>
       </c>
       <c r="B194" t="n">
-        <v>-0.006094406739692357</v>
+        <v>-0.006094424078147824</v>
       </c>
       <c r="C194" t="n">
-        <v>0.4170077940065325</v>
+        <v>0.4170077932826105</v>
       </c>
       <c r="D194" t="n">
-        <v>1.053206130883687</v>
+        <v>1.452364388202227</v>
       </c>
     </row>
     <row r="195">
@@ -3149,13 +3149,13 @@
         <v>45382</v>
       </c>
       <c r="B195" t="n">
-        <v>0</v>
+        <v>0.001846107522461374</v>
       </c>
       <c r="C195" t="n">
-        <v>0.4108347904686717</v>
+        <v>0.4108347900847243</v>
       </c>
       <c r="D195" t="n">
-        <v>1.053206130883687</v>
+        <v>1.455045609024643</v>
       </c>
     </row>
     <row r="196">
@@ -3163,13 +3163,13 @@
         <v>45412</v>
       </c>
       <c r="B196" t="n">
-        <v>0</v>
+        <v>-0.005841766649395732</v>
       </c>
       <c r="C196" t="n">
-        <v>0.3731656502250368</v>
+        <v>0.373165698590766</v>
       </c>
       <c r="D196" t="n">
-        <v>1.053206130883687</v>
+        <v>1.446545572112493</v>
       </c>
     </row>
     <row r="197">
@@ -3177,13 +3177,13 @@
         <v>45443</v>
       </c>
       <c r="B197" t="n">
-        <v>0.009478535051071395</v>
+        <v>0.009478916124101594</v>
       </c>
       <c r="C197" t="n">
-        <v>0.3653139762978134</v>
+        <v>0.3653140235050353</v>
       </c>
       <c r="D197" t="n">
-        <v>1.063188982111271</v>
+        <v>1.460257256260238</v>
       </c>
     </row>
     <row r="198">
@@ -3191,13 +3191,13 @@
         <v>45473</v>
       </c>
       <c r="B198" t="n">
-        <v>0</v>
+        <v>0.004444778018474317</v>
       </c>
       <c r="C198" t="n">
-        <v>0.3452966387000535</v>
+        <v>0.3452966930568737</v>
       </c>
       <c r="D198" t="n">
-        <v>1.063188982111271</v>
+        <v>1.466747775614181</v>
       </c>
     </row>
     <row r="199">
@@ -3205,13 +3205,13 @@
         <v>45504</v>
       </c>
       <c r="B199" t="n">
-        <v>0</v>
+        <v>0.01549908410188583</v>
       </c>
       <c r="C199" t="n">
-        <v>0.3486483129332825</v>
+        <v>0.3486483152489209</v>
       </c>
       <c r="D199" t="n">
-        <v>1.063188982111271</v>
+        <v>1.489481022744679</v>
       </c>
     </row>
     <row r="200">
@@ -3219,13 +3219,13 @@
         <v>45535</v>
       </c>
       <c r="B200" t="n">
-        <v>0</v>
+        <v>0.01115889126586952</v>
       </c>
       <c r="C200" t="n">
-        <v>0.4063301478433092</v>
+        <v>0.4063301454600563</v>
       </c>
       <c r="D200" t="n">
-        <v>1.063188982111271</v>
+        <v>1.506101979520063</v>
       </c>
     </row>
     <row r="201">
@@ -3233,13 +3233,13 @@
         <v>45565</v>
       </c>
       <c r="B201" t="n">
-        <v>0</v>
+        <v>0.00606654115306707</v>
       </c>
       <c r="C201" t="n">
-        <v>0.6668517415603471</v>
+        <v>0.6668517401264512</v>
       </c>
       <c r="D201" t="n">
-        <v>1.063188982111271</v>
+        <v>1.515238809159537</v>
       </c>
     </row>
     <row r="202">
@@ -3247,13 +3247,13 @@
         <v>45596</v>
       </c>
       <c r="B202" t="n">
-        <v>-0.02140391479422332</v>
+        <v>-0.02140398851302335</v>
       </c>
       <c r="C202" t="n">
-        <v>0.6703036750058322</v>
+        <v>0.6703037135474887</v>
       </c>
       <c r="D202" t="n">
-        <v>1.040432575728004</v>
+        <v>1.482806655093799</v>
       </c>
     </row>
     <row r="203">
@@ -3261,13 +3261,13 @@
         <v>45626</v>
       </c>
       <c r="B203" t="n">
-        <v>0</v>
+        <v>0.00800959458893071</v>
       </c>
       <c r="C203" t="n">
-        <v>0.6557384519672884</v>
+        <v>0.6557384931312087</v>
       </c>
       <c r="D203" t="n">
-        <v>1.040432575728004</v>
+        <v>1.494683335254869</v>
       </c>
     </row>
     <row r="204">
@@ -3275,13 +3275,13 @@
         <v>45657</v>
       </c>
       <c r="B204" t="n">
-        <v>0</v>
+        <v>-0.01338082327620956</v>
       </c>
       <c r="C204" t="n">
-        <v>0.6526485150819625</v>
+        <v>0.6526485139869798</v>
       </c>
       <c r="D204" t="n">
-        <v>1.040432575728004</v>
+        <v>1.474683241691928</v>
       </c>
     </row>
     <row r="205">
@@ -3289,13 +3289,13 @@
         <v>45688</v>
       </c>
       <c r="B205" t="n">
-        <v>0.004495662980923064</v>
+        <v>0.004495607646102956</v>
       </c>
       <c r="C205" t="n">
-        <v>0.373483049335197</v>
+        <v>0.3734830498707288</v>
       </c>
       <c r="D205" t="n">
-        <v>1.045110009942851</v>
+        <v>1.481312838948858</v>
       </c>
     </row>
     <row r="206">
@@ -3303,13 +3303,13 @@
         <v>45716</v>
       </c>
       <c r="B206" t="n">
-        <v>0.01240927195260916</v>
+        <v>0.0124094361360329</v>
       </c>
       <c r="C206" t="n">
-        <v>0.3704364135738338</v>
+        <v>0.3704364142786817</v>
       </c>
       <c r="D206" t="n">
-        <v>1.058079064276626</v>
+        <v>1.49969509602128</v>
       </c>
     </row>
     <row r="207">
@@ -3317,13 +3317,13 @@
         <v>45747</v>
       </c>
       <c r="B207" t="n">
-        <v>0.003361775607643689</v>
+        <v>0.003361622591107644</v>
       </c>
       <c r="C207" t="n">
-        <v>0.6124763537918628</v>
+        <v>0.6124763549408597</v>
       </c>
       <c r="D207" t="n">
-        <v>1.06163608866587</v>
+        <v>1.504736504935838</v>
       </c>
     </row>
     <row r="208">
@@ -3331,13 +3331,13 @@
         <v>45777</v>
       </c>
       <c r="B208" t="n">
-        <v>0.00607095047253387</v>
+        <v>0.006070888318446184</v>
       </c>
       <c r="C208" t="n">
-        <v>0.3727766257451262</v>
+        <v>0.3727766263168697</v>
       </c>
       <c r="D208" t="n">
-        <v>1.068081228780015</v>
+        <v>1.513871592205993</v>
       </c>
     </row>
     <row r="209">
@@ -3345,13 +3345,13 @@
         <v>45808</v>
       </c>
       <c r="B209" t="n">
-        <v>0</v>
+        <v>-0.009498202779070524</v>
       </c>
       <c r="C209" t="n">
-        <v>0.6803828556420777</v>
+        <v>0.6803828127439544</v>
       </c>
       <c r="D209" t="n">
-        <v>1.068081228780015</v>
+        <v>1.499492532841746</v>
       </c>
     </row>
     <row r="210">
@@ -3359,13 +3359,13 @@
         <v>45838</v>
       </c>
       <c r="B210" t="n">
-        <v>0</v>
+        <v>0.01416851133336213</v>
       </c>
       <c r="C210" t="n">
-        <v>0.6742897748903307</v>
+        <v>0.6742897728086141</v>
       </c>
       <c r="D210" t="n">
-        <v>1.068081228780015</v>
+        <v>1.520738109787606</v>
       </c>
     </row>
     <row r="211">
@@ -3373,13 +3373,13 @@
         <v>45869</v>
       </c>
       <c r="B211" t="n">
-        <v>-0.00257344253468376</v>
+        <v>-0.002573419859855191</v>
       </c>
       <c r="C211" t="n">
-        <v>0.6458931195776387</v>
+        <v>0.6458930750727423</v>
       </c>
       <c r="D211" t="n">
-        <v>1.065332583115375</v>
+        <v>1.51682461213424</v>
       </c>
     </row>
     <row r="212">
@@ -3387,13 +3387,13 @@
         <v>45900</v>
       </c>
       <c r="B212" t="n">
-        <v>0</v>
+        <v>0.007294774425237198</v>
       </c>
       <c r="C212" t="n">
-        <v>0.352199534136267</v>
+        <v>0.3521994855169084</v>
       </c>
       <c r="D212" t="n">
-        <v>1.065332583115375</v>
+        <v>1.527889505522407</v>
       </c>
     </row>
     <row r="213">
@@ -3401,13 +3401,13 @@
         <v>45930</v>
       </c>
       <c r="B213" t="n">
-        <v>0</v>
+        <v>0.005381064229059884</v>
       </c>
       <c r="C213" t="n">
-        <v>0.3589970463410664</v>
+        <v>0.358997048309121</v>
       </c>
       <c r="D213" t="n">
-        <v>1.065332583115375</v>
+        <v>1.53611117708653</v>
       </c>
     </row>
     <row r="214">
@@ -3415,13 +3415,13 @@
         <v>45961</v>
       </c>
       <c r="B214" t="n">
-        <v>0.004794486641753321</v>
+        <v>0.004794625100286095</v>
       </c>
       <c r="C214" t="n">
-        <v>0.3564345375402613</v>
+        <v>0.3564345396470449</v>
       </c>
       <c r="D214" t="n">
-        <v>1.070440305954146</v>
+        <v>1.543476254293019</v>
       </c>
     </row>
     <row r="215">
@@ -3429,13 +3429,13 @@
         <v>45991</v>
       </c>
       <c r="B215" t="n">
-        <v>0</v>
+        <v>0.003875133070003339</v>
       </c>
       <c r="C215" t="n">
-        <v>0.6010373223671923</v>
+        <v>0.6010373247690779</v>
       </c>
       <c r="D215" t="n">
-        <v>1.070440305954146</v>
+        <v>1.549457430168795</v>
       </c>
     </row>
     <row r="216">
@@ -3443,13 +3443,13 @@
         <v>46022</v>
       </c>
       <c r="B216" t="n">
-        <v>0</v>
+        <v>-1.536685491350907e-05</v>
       </c>
       <c r="C216" t="n">
-        <v>0.5918640725587734</v>
+        <v>0.5918640754638129</v>
       </c>
       <c r="D216" t="n">
-        <v>1.070440305954146</v>
+        <v>1.549433619881271</v>
       </c>
     </row>
     <row r="217">
@@ -3457,13 +3457,13 @@
         <v>46053</v>
       </c>
       <c r="B217" t="n">
-        <v>0</v>
+        <v>-0.001268026133853815</v>
       </c>
       <c r="C217" t="n">
-        <v>0.5947948426930394</v>
+        <v>0.5947948454328205</v>
       </c>
       <c r="D217" t="n">
-        <v>1.070440305954146</v>
+        <v>1.54746889755859</v>
       </c>
     </row>
     <row r="218">
@@ -3471,13 +3471,13 @@
         <v>46081</v>
       </c>
       <c r="B218" t="n">
-        <v>0</v>
+        <v>0.01274850271011552</v>
       </c>
       <c r="C218" t="n">
-        <v>0.5639298629423446</v>
+        <v>0.5639298673802193</v>
       </c>
       <c r="D218" t="n">
-        <v>1.070440305954146</v>
+        <v>1.567196808992935</v>
       </c>
     </row>
     <row r="219">
@@ -3485,13 +3485,13 @@
         <v>46112</v>
       </c>
       <c r="B219" t="n">
-        <v>0</v>
+        <v>-0.008330685097882422</v>
       </c>
       <c r="C219" t="n">
-        <v>0.5523774415163224</v>
+        <v>0.5523774465821596</v>
       </c>
       <c r="D219" t="n">
-        <v>1.070440305954146</v>
+        <v>1.554140985890809</v>
       </c>
     </row>
     <row r="220">
@@ -3499,13 +3499,13 @@
         <v>46142</v>
       </c>
       <c r="B220" t="n">
-        <v>0</v>
+        <v>0.003069148806222267</v>
       </c>
       <c r="C220" t="n">
         <v>0.25</v>
       </c>
       <c r="D220" t="n">
-        <v>1.070440305954146</v>
+        <v>1.558910875842357</v>
       </c>
     </row>
   </sheetData>
